--- a/2026年度物件表_KMN置換.xlsx
+++ b/2026年度物件表_KMN置換.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-24780" yWindow="0" windowWidth="21600" windowHeight="15585" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026年度担当者物件表  20260127" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="水曜日金属（行ってるとこコバ）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="水曜日金属収集表  (改定)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="水曜日金属収集表  (uejii)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="水曜日金属収集表 " sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="水曜日可燃収集表 (20250709)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="土曜日物件表 20250624" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ガラ集物件（20250709）" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="段ボール週間予定表" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ダンボール収集表" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026年度担当者物件表  20260127" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属（行ってるとこコバ）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (改定)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表  (uejii)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日金属収集表 " sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="水曜日可燃収集表 (20250709)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="土曜日物件表 20250624" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ガラ集物件（20250709）" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="段ボール週間予定表" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ダンボール収集表" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId11"/>
-    <externalReference r:id="rId12"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+    <externalReference xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
   </externalReferences>
   <definedNames>
     <definedName name="休日出勤？">#REF!</definedName>
@@ -2622,8 +2622,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="H29年度担当者物件表  (改訂版)"/>
       <sheetName val="H29年度①担当物件 月曜日"/>
@@ -2691,8 +2691,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="H29年度①担当物件 月曜日"/>
       <sheetName val="H29年度①担当物件 火曜日"/>
@@ -3197,37 +3197,37 @@
       </c>
       <c r="K1" s="203" t="inlineStr">
         <is>
+          <t>水曜日</t>
+        </is>
+      </c>
+      <c r="L1" s="204" t="inlineStr">
+        <is>
+          <t>木曜日</t>
+        </is>
+      </c>
+      <c r="M1" s="203" t="inlineStr">
+        <is>
+          <t>金曜日</t>
+        </is>
+      </c>
+      <c r="N1" s="202" t="inlineStr">
+        <is>
+          <t>土曜日</t>
+        </is>
+      </c>
+      <c r="O1" s="202" t="inlineStr">
+        <is>
+          <t>日曜日</t>
+        </is>
+      </c>
+      <c r="P1" s="202" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L1" s="204" t="inlineStr">
-        <is>
-          <t>水曜日</t>
-        </is>
-      </c>
-      <c r="M1" s="203" t="inlineStr">
+      <c r="Q1" s="203" t="inlineStr">
         <is>
           <t>木曜段紙</t>
-        </is>
-      </c>
-      <c r="N1" s="202" t="inlineStr">
-        <is>
-          <t>木曜日</t>
-        </is>
-      </c>
-      <c r="O1" s="202" t="inlineStr">
-        <is>
-          <t>金曜日</t>
-        </is>
-      </c>
-      <c r="P1" s="202" t="inlineStr">
-        <is>
-          <t>土曜日</t>
-        </is>
-      </c>
-      <c r="Q1" s="203" t="inlineStr">
-        <is>
-          <t>日曜日</t>
         </is>
       </c>
       <c r="R1" s="205" t="inlineStr">
@@ -3317,13 +3317,13 @@
       </c>
       <c r="K2" s="211" t="n"/>
       <c r="L2" s="210" t="n"/>
-      <c r="M2" s="211" t="n"/>
+      <c r="M2" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N2" s="211" t="n"/>
-      <c r="O2" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O2" s="211" t="n"/>
       <c r="P2" s="211" t="n"/>
       <c r="Q2" s="233" t="n"/>
       <c r="R2" s="212" t="n"/>
@@ -3378,25 +3378,25 @@
       <c r="H3" s="211" t="n"/>
       <c r="I3" s="211" t="n"/>
       <c r="J3" s="211" t="n"/>
-      <c r="K3" s="211" t="inlineStr">
-        <is>
-          <t>金属</t>
-        </is>
-      </c>
+      <c r="K3" s="211" t="n"/>
       <c r="L3" s="210" t="n"/>
       <c r="M3" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N3" s="211" t="n"/>
+      <c r="O3" s="211" t="n"/>
+      <c r="P3" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
+      <c r="Q3" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N3" s="211" t="n"/>
-      <c r="O3" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P3" s="211" t="n"/>
-      <c r="Q3" s="233" t="n"/>
       <c r="R3" s="212" t="n"/>
       <c r="S3" s="233" t="n"/>
       <c r="T3" s="211" t="n"/>
@@ -3496,17 +3496,17 @@
       <c r="L4" s="210" t="n"/>
       <c r="M4" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N4" s="211" t="n"/>
+      <c r="O4" s="211" t="n"/>
+      <c r="P4" s="211" t="n"/>
+      <c r="Q4" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N4" s="211" t="n"/>
-      <c r="O4" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P4" s="211" t="n"/>
-      <c r="Q4" s="233" t="n"/>
       <c r="R4" s="212" t="n"/>
       <c r="S4" s="233" t="n"/>
       <c r="T4" s="211" t="n"/>
@@ -3595,13 +3595,13 @@
       </c>
       <c r="J5" s="211" t="n"/>
       <c r="K5" s="211" t="n"/>
-      <c r="L5" s="210" t="n"/>
+      <c r="L5" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M5" s="211" t="n"/>
-      <c r="N5" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N5" s="211" t="n"/>
       <c r="O5" s="211" t="n"/>
       <c r="P5" s="211" t="n"/>
       <c r="Q5" s="233" t="n"/>
@@ -3669,28 +3669,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K6" s="211" t="n"/>
+      <c r="K6" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L6" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M6" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M6" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N6" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O6" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P6" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O6" s="211" t="n"/>
+      <c r="P6" s="211" t="n"/>
       <c r="Q6" s="233" t="n"/>
       <c r="R6" s="212" t="n"/>
       <c r="S6" s="233" t="n"/>
@@ -3785,28 +3785,28 @@
       </c>
       <c r="K7" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L7" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M7" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N7" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O7" s="211" t="n"/>
+      <c r="P7" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L7" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M7" s="211" t="n"/>
-      <c r="N7" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O7" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P7" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
         </is>
       </c>
       <c r="Q7" s="233" t="n"/>
@@ -3935,28 +3935,28 @@
       </c>
       <c r="K8" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L8" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M8" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N8" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O8" s="211" t="n"/>
+      <c r="P8" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L8" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M8" s="211" t="n"/>
-      <c r="N8" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O8" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P8" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
         </is>
       </c>
       <c r="Q8" s="233" t="n"/>
@@ -4075,24 +4075,24 @@
         </is>
       </c>
       <c r="J9" s="211" t="n"/>
-      <c r="K9" s="211" t="n"/>
-      <c r="L9" s="210" t="inlineStr">
+      <c r="K9" s="211" t="inlineStr">
         <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="M9" s="211" t="n"/>
-      <c r="N9" s="211" t="n"/>
-      <c r="O9" s="211" t="inlineStr">
+      <c r="L9" s="210" t="n"/>
+      <c r="M9" s="211" t="inlineStr">
         <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="P9" s="211" t="inlineStr">
+      <c r="N9" s="211" t="inlineStr">
         <is>
           <t>段紙</t>
         </is>
       </c>
+      <c r="O9" s="211" t="n"/>
+      <c r="P9" s="211" t="n"/>
       <c r="Q9" s="233" t="n"/>
       <c r="R9" s="212" t="n"/>
       <c r="S9" s="233" t="n"/>
@@ -4197,24 +4197,24 @@
         </is>
       </c>
       <c r="J10" s="211" t="n"/>
-      <c r="K10" s="211" t="n"/>
-      <c r="L10" s="210" t="inlineStr">
+      <c r="K10" s="211" t="inlineStr">
         <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="M10" s="211" t="n"/>
-      <c r="N10" s="211" t="n"/>
-      <c r="O10" s="211" t="inlineStr">
+      <c r="L10" s="210" t="n"/>
+      <c r="M10" s="211" t="inlineStr">
         <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="P10" s="211" t="inlineStr">
+      <c r="N10" s="211" t="inlineStr">
         <is>
           <t>段紙</t>
         </is>
       </c>
+      <c r="O10" s="211" t="n"/>
+      <c r="P10" s="211" t="n"/>
       <c r="Q10" s="233" t="n"/>
       <c r="R10" s="212" t="n"/>
       <c r="S10" s="233" t="n"/>
@@ -4319,24 +4319,24 @@
         </is>
       </c>
       <c r="J11" s="220" t="n"/>
-      <c r="K11" s="220" t="n"/>
-      <c r="L11" s="221" t="inlineStr">
+      <c r="K11" s="220" t="inlineStr">
         <is>
           <t>PET アルミ</t>
         </is>
       </c>
-      <c r="M11" s="220" t="n"/>
-      <c r="N11" s="220" t="n"/>
-      <c r="O11" s="219" t="inlineStr">
+      <c r="L11" s="221" t="n"/>
+      <c r="M11" s="220" t="inlineStr">
         <is>
           <t>PET アルミ</t>
         </is>
       </c>
-      <c r="P11" s="219" t="inlineStr">
+      <c r="N11" s="220" t="inlineStr">
         <is>
           <t>PET アルミ</t>
         </is>
       </c>
+      <c r="O11" s="219" t="n"/>
+      <c r="P11" s="219" t="n"/>
       <c r="Q11" s="233" t="n"/>
       <c r="R11" s="212" t="n"/>
       <c r="S11" s="233" t="n"/>
@@ -4441,19 +4441,19 @@
         </is>
       </c>
       <c r="J12" s="211" t="n"/>
-      <c r="K12" s="211" t="n"/>
-      <c r="L12" s="210" t="inlineStr">
+      <c r="K12" s="211" t="inlineStr">
         <is>
           <t>発泡</t>
         </is>
       </c>
-      <c r="M12" s="211" t="n"/>
+      <c r="L12" s="210" t="n"/>
+      <c r="M12" s="211" t="inlineStr">
+        <is>
+          <t>発泡</t>
+        </is>
+      </c>
       <c r="N12" s="211" t="n"/>
-      <c r="O12" s="211" t="inlineStr">
-        <is>
-          <t>発泡</t>
-        </is>
-      </c>
+      <c r="O12" s="211" t="n"/>
       <c r="P12" s="211" t="n"/>
       <c r="Q12" s="233" t="n"/>
       <c r="R12" s="212" t="n"/>
@@ -4559,29 +4559,29 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K13" s="211" t="n"/>
+      <c r="K13" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L13" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
+          <t>K-</t>
         </is>
       </c>
       <c r="M13" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N13" s="211" t="n"/>
+      <c r="O13" s="211" t="n"/>
+      <c r="P13" s="211" t="n"/>
+      <c r="Q13" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N13" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O13" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P13" s="211" t="n"/>
-      <c r="Q13" s="233" t="n"/>
       <c r="R13" s="212" t="n"/>
       <c r="S13" s="233" t="n"/>
       <c r="T13" s="211" t="n"/>
@@ -4648,13 +4648,13 @@
       <c r="J14" s="211" t="n"/>
       <c r="K14" s="211" t="n"/>
       <c r="L14" s="210" t="n"/>
-      <c r="M14" s="211" t="n"/>
+      <c r="M14" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N14" s="211" t="n"/>
-      <c r="O14" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O14" s="211" t="n"/>
       <c r="P14" s="211" t="n"/>
       <c r="Q14" s="233" t="n"/>
       <c r="R14" s="212" t="n"/>
@@ -4705,12 +4705,12 @@
       <c r="H15" s="211" t="n"/>
       <c r="I15" s="211" t="n"/>
       <c r="J15" s="211" t="n"/>
-      <c r="K15" s="211" t="n"/>
-      <c r="L15" s="210" t="inlineStr">
+      <c r="K15" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L15" s="210" t="n"/>
       <c r="M15" s="211" t="n"/>
       <c r="N15" s="211" t="n"/>
       <c r="O15" s="211" t="n"/>
@@ -4782,13 +4782,13 @@
       </c>
       <c r="K16" s="211" t="n"/>
       <c r="L16" s="210" t="n"/>
-      <c r="M16" s="211" t="n"/>
+      <c r="M16" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N16" s="211" t="n"/>
-      <c r="O16" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O16" s="211" t="n"/>
       <c r="P16" s="211" t="n"/>
       <c r="Q16" s="233" t="n"/>
       <c r="R16" s="212" t="n"/>
@@ -4847,19 +4847,19 @@
         </is>
       </c>
       <c r="J17" s="211" t="n"/>
-      <c r="K17" s="211" t="n"/>
-      <c r="L17" s="210" t="inlineStr">
+      <c r="K17" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M17" s="211" t="n"/>
+      <c r="L17" s="210" t="n"/>
+      <c r="M17" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N17" s="211" t="n"/>
-      <c r="O17" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O17" s="211" t="n"/>
       <c r="P17" s="211" t="n"/>
       <c r="Q17" s="233" t="n"/>
       <c r="R17" s="212" t="n"/>
@@ -4922,20 +4922,20 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K18" s="211" t="inlineStr">
+      <c r="K18" s="211" t="n"/>
+      <c r="L18" s="210" t="n"/>
+      <c r="M18" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N18" s="211" t="n"/>
+      <c r="O18" s="211" t="n"/>
+      <c r="P18" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L18" s="210" t="n"/>
-      <c r="M18" s="211" t="n"/>
-      <c r="N18" s="211" t="n"/>
-      <c r="O18" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P18" s="211" t="n"/>
       <c r="Q18" s="233" t="n"/>
       <c r="R18" s="222" t="inlineStr">
         <is>
@@ -4999,13 +4999,13 @@
       </c>
       <c r="K19" s="211" t="n"/>
       <c r="L19" s="210" t="n"/>
-      <c r="M19" s="211" t="n"/>
+      <c r="M19" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N19" s="211" t="n"/>
-      <c r="O19" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O19" s="211" t="n"/>
       <c r="P19" s="211" t="n"/>
       <c r="Q19" s="233" t="n"/>
       <c r="R19" s="212" t="n"/>
@@ -5061,13 +5061,13 @@
       <c r="I20" s="211" t="n"/>
       <c r="J20" s="211" t="n"/>
       <c r="K20" s="211" t="n"/>
-      <c r="L20" s="210" t="n"/>
+      <c r="L20" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M20" s="211" t="n"/>
-      <c r="N20" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N20" s="211" t="n"/>
       <c r="O20" s="211" t="n"/>
       <c r="P20" s="211" t="n"/>
       <c r="Q20" s="233" t="n"/>
@@ -5121,13 +5121,13 @@
       <c r="J21" s="211" t="n"/>
       <c r="K21" s="211" t="n"/>
       <c r="L21" s="210" t="n"/>
-      <c r="M21" s="211" t="n"/>
+      <c r="M21" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N21" s="211" t="n"/>
-      <c r="O21" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O21" s="211" t="n"/>
       <c r="P21" s="211" t="n"/>
       <c r="Q21" s="233" t="n"/>
       <c r="R21" s="212" t="n"/>
@@ -5186,20 +5186,20 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K22" s="211" t="inlineStr">
+      <c r="K22" s="211" t="n"/>
+      <c r="L22" s="210" t="n"/>
+      <c r="M22" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N22" s="211" t="n"/>
+      <c r="O22" s="211" t="n"/>
+      <c r="P22" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L22" s="210" t="n"/>
-      <c r="M22" s="211" t="n"/>
-      <c r="N22" s="211" t="n"/>
-      <c r="O22" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P22" s="211" t="n"/>
       <c r="Q22" s="233" t="n"/>
       <c r="R22" s="212" t="n"/>
       <c r="S22" s="233" t="n"/>
@@ -5261,17 +5261,17 @@
       <c r="L23" s="210" t="n"/>
       <c r="M23" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N23" s="211" t="n"/>
+      <c r="O23" s="211" t="n"/>
+      <c r="P23" s="211" t="n"/>
+      <c r="Q23" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N23" s="211" t="n"/>
-      <c r="O23" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P23" s="211" t="n"/>
-      <c r="Q23" s="233" t="n"/>
       <c r="R23" s="212" t="n"/>
       <c r="S23" s="233" t="n"/>
       <c r="T23" s="211" t="n"/>
@@ -5326,13 +5326,13 @@
       <c r="J24" s="211" t="n"/>
       <c r="K24" s="211" t="n"/>
       <c r="L24" s="210" t="n"/>
-      <c r="M24" s="211" t="n"/>
+      <c r="M24" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N24" s="211" t="n"/>
-      <c r="O24" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O24" s="211" t="n"/>
       <c r="P24" s="211" t="n"/>
       <c r="Q24" s="233" t="n"/>
       <c r="R24" s="212" t="n"/>
@@ -5402,17 +5402,17 @@
       <c r="L25" s="210" t="n"/>
       <c r="M25" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N25" s="211" t="n"/>
+      <c r="O25" s="211" t="n"/>
+      <c r="P25" s="211" t="n"/>
+      <c r="Q25" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N25" s="211" t="n"/>
-      <c r="O25" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P25" s="211" t="n"/>
-      <c r="Q25" s="233" t="n"/>
       <c r="R25" s="212" t="n"/>
       <c r="S25" s="233" t="n"/>
       <c r="T25" s="211" t="n"/>
@@ -5480,19 +5480,19 @@
         </is>
       </c>
       <c r="J26" s="211" t="n"/>
-      <c r="K26" s="211" t="n"/>
-      <c r="L26" s="210" t="inlineStr">
+      <c r="K26" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M26" s="211" t="n"/>
+      <c r="L26" s="210" t="n"/>
+      <c r="M26" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N26" s="211" t="n"/>
-      <c r="O26" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O26" s="211" t="n"/>
       <c r="P26" s="211" t="n"/>
       <c r="Q26" s="233" t="n"/>
       <c r="R26" s="212" t="n"/>
@@ -5560,13 +5560,13 @@
       <c r="J27" s="211" t="n"/>
       <c r="K27" s="211" t="n"/>
       <c r="L27" s="210" t="n"/>
-      <c r="M27" s="211" t="n"/>
+      <c r="M27" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N27" s="211" t="n"/>
-      <c r="O27" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O27" s="211" t="n"/>
       <c r="P27" s="211" t="n"/>
       <c r="Q27" s="233" t="n"/>
       <c r="R27" s="212" t="n"/>
@@ -5636,28 +5636,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K28" s="211" t="n"/>
+      <c r="K28" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L28" s="210" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M28" s="211" t="inlineStr">
+        <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M28" s="211" t="n"/>
       <c r="N28" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O28" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P28" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O28" s="211" t="n"/>
+      <c r="P28" s="211" t="n"/>
       <c r="Q28" s="233" t="n"/>
       <c r="R28" s="212" t="inlineStr">
         <is>
@@ -5740,13 +5740,13 @@
       <c r="J29" s="211" t="n"/>
       <c r="K29" s="211" t="n"/>
       <c r="L29" s="210" t="n"/>
-      <c r="M29" s="211" t="n"/>
+      <c r="M29" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N29" s="211" t="n"/>
-      <c r="O29" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O29" s="211" t="n"/>
       <c r="P29" s="211" t="n"/>
       <c r="Q29" s="233" t="n"/>
       <c r="R29" s="212" t="n"/>
@@ -5878,12 +5878,12 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K31" s="211" t="n"/>
-      <c r="L31" s="210" t="inlineStr">
+      <c r="K31" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L31" s="210" t="n"/>
       <c r="M31" s="211" t="n"/>
       <c r="N31" s="211" t="n"/>
       <c r="O31" s="211" t="n"/>
@@ -5957,13 +5957,13 @@
       </c>
       <c r="J32" s="211" t="n"/>
       <c r="K32" s="211" t="n"/>
-      <c r="L32" s="210" t="n"/>
+      <c r="L32" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M32" s="211" t="n"/>
-      <c r="N32" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N32" s="211" t="n"/>
       <c r="O32" s="211" t="n"/>
       <c r="P32" s="211" t="n"/>
       <c r="Q32" s="233" t="n"/>
@@ -6041,26 +6041,26 @@
       </c>
       <c r="K33" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L33" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M33" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N33" s="211" t="n"/>
+      <c r="O33" s="211" t="n"/>
+      <c r="P33" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L33" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M33" s="211" t="n"/>
-      <c r="N33" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O33" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P33" s="211" t="n"/>
       <c r="Q33" s="233" t="n"/>
       <c r="R33" s="212" t="n"/>
       <c r="S33" s="233" t="n"/>
@@ -6135,13 +6135,13 @@
       <c r="J34" s="211" t="n"/>
       <c r="K34" s="211" t="n"/>
       <c r="L34" s="210" t="n"/>
-      <c r="M34" s="211" t="n"/>
+      <c r="M34" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N34" s="211" t="n"/>
-      <c r="O34" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O34" s="211" t="n"/>
       <c r="P34" s="211" t="n"/>
       <c r="Q34" s="233" t="n"/>
       <c r="R34" s="212" t="n"/>
@@ -6200,19 +6200,19 @@
       </c>
       <c r="I35" s="211" t="n"/>
       <c r="J35" s="211" t="n"/>
-      <c r="K35" s="211" t="n"/>
-      <c r="L35" s="210" t="inlineStr">
+      <c r="K35" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M35" s="211" t="n"/>
+      <c r="L35" s="210" t="n"/>
+      <c r="M35" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N35" s="211" t="n"/>
-      <c r="O35" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O35" s="211" t="n"/>
       <c r="P35" s="211" t="n"/>
       <c r="Q35" s="233" t="n"/>
       <c r="R35" s="212" t="n"/>
@@ -6283,7 +6283,11 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K36" s="211" t="n"/>
+      <c r="K36" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L36" s="210" t="inlineStr">
         <is>
           <t>N-</t>
@@ -6291,25 +6295,21 @@
       </c>
       <c r="M36" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N36" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O36" s="211" t="n"/>
+      <c r="P36" s="211" t="n"/>
+      <c r="Q36" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N36" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O36" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P36" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q36" s="233" t="n"/>
       <c r="R36" s="212" t="n"/>
       <c r="S36" s="233" t="n"/>
       <c r="T36" s="211" t="n"/>
@@ -6384,13 +6384,13 @@
       <c r="J37" s="211" t="n"/>
       <c r="K37" s="211" t="n"/>
       <c r="L37" s="210" t="n"/>
-      <c r="M37" s="211" t="n"/>
+      <c r="M37" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N37" s="211" t="n"/>
-      <c r="O37" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O37" s="211" t="n"/>
       <c r="P37" s="211" t="n"/>
       <c r="Q37" s="233" t="n"/>
       <c r="R37" s="212" t="n"/>
@@ -6445,20 +6445,20 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K38" s="211" t="inlineStr">
+      <c r="K38" s="211" t="n"/>
+      <c r="L38" s="210" t="n"/>
+      <c r="M38" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N38" s="211" t="n"/>
+      <c r="O38" s="211" t="n"/>
+      <c r="P38" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L38" s="210" t="n"/>
-      <c r="M38" s="211" t="n"/>
-      <c r="N38" s="211" t="n"/>
-      <c r="O38" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P38" s="211" t="n"/>
       <c r="Q38" s="233" t="n"/>
       <c r="R38" s="212" t="inlineStr">
         <is>
@@ -6524,20 +6524,20 @@
       </c>
       <c r="I39" s="211" t="n"/>
       <c r="J39" s="211" t="n"/>
-      <c r="K39" s="211" t="inlineStr">
+      <c r="K39" s="211" t="n"/>
+      <c r="L39" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M39" s="211" t="n"/>
+      <c r="N39" s="211" t="n"/>
+      <c r="O39" s="211" t="n"/>
+      <c r="P39" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L39" s="210" t="n"/>
-      <c r="M39" s="211" t="n"/>
-      <c r="N39" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O39" s="211" t="n"/>
-      <c r="P39" s="211" t="n"/>
       <c r="Q39" s="233" t="n"/>
       <c r="R39" s="212" t="n"/>
       <c r="S39" s="233" t="n"/>
@@ -6591,20 +6591,20 @@
       <c r="H40" s="211" t="n"/>
       <c r="I40" s="211" t="n"/>
       <c r="J40" s="211" t="n"/>
-      <c r="K40" s="211" t="n"/>
-      <c r="L40" s="210" t="inlineStr">
+      <c r="K40" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L40" s="210" t="n"/>
       <c r="M40" s="211" t="n"/>
-      <c r="N40" s="211" t="n"/>
+      <c r="N40" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="O40" s="211" t="n"/>
-      <c r="P40" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="P40" s="211" t="n"/>
       <c r="Q40" s="233" t="n"/>
       <c r="R40" s="212" t="n"/>
       <c r="S40" s="233" t="n"/>
@@ -6659,13 +6659,13 @@
       <c r="I41" s="211" t="n"/>
       <c r="J41" s="211" t="n"/>
       <c r="K41" s="211" t="n"/>
-      <c r="L41" s="210" t="n"/>
+      <c r="L41" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M41" s="211" t="n"/>
-      <c r="N41" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N41" s="211" t="n"/>
       <c r="O41" s="211" t="n"/>
       <c r="P41" s="211" t="n"/>
       <c r="Q41" s="233" t="n"/>
@@ -6719,13 +6719,13 @@
       <c r="J42" s="211" t="n"/>
       <c r="K42" s="211" t="n"/>
       <c r="L42" s="210" t="n"/>
-      <c r="M42" s="211" t="n"/>
+      <c r="M42" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N42" s="211" t="n"/>
-      <c r="O42" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O42" s="211" t="n"/>
       <c r="P42" s="211" t="n"/>
       <c r="Q42" s="233" t="n"/>
       <c r="R42" s="212" t="n"/>
@@ -6776,12 +6776,12 @@
       <c r="H43" s="211" t="n"/>
       <c r="I43" s="211" t="n"/>
       <c r="J43" s="211" t="n"/>
-      <c r="K43" s="211" t="n"/>
-      <c r="L43" s="210" t="inlineStr">
+      <c r="K43" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L43" s="210" t="n"/>
       <c r="M43" s="211" t="n"/>
       <c r="N43" s="211" t="n"/>
       <c r="O43" s="211" t="n"/>
@@ -6835,12 +6835,12 @@
       <c r="H44" s="211" t="n"/>
       <c r="I44" s="211" t="n"/>
       <c r="J44" s="211" t="n"/>
-      <c r="K44" s="211" t="n"/>
-      <c r="L44" s="210" t="inlineStr">
+      <c r="K44" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L44" s="210" t="n"/>
       <c r="M44" s="211" t="n"/>
       <c r="N44" s="211" t="n"/>
       <c r="O44" s="211" t="n"/>
@@ -6906,28 +6906,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K45" s="211" t="n"/>
+      <c r="K45" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L45" s="210" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M45" s="211" t="n"/>
+      <c r="M45" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N45" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O45" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P45" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O45" s="211" t="n"/>
+      <c r="P45" s="211" t="n"/>
       <c r="Q45" s="233" t="n"/>
       <c r="R45" s="212" t="n"/>
       <c r="S45" s="233" t="n"/>
@@ -7003,13 +7003,13 @@
       <c r="J46" s="211" t="n"/>
       <c r="K46" s="211" t="n"/>
       <c r="L46" s="210" t="n"/>
-      <c r="M46" s="211" t="n"/>
+      <c r="M46" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N46" s="211" t="n"/>
-      <c r="O46" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O46" s="211" t="n"/>
       <c r="P46" s="211" t="n"/>
       <c r="Q46" s="233" t="n"/>
       <c r="R46" s="212" t="n"/>
@@ -7062,13 +7062,13 @@
       <c r="J47" s="211" t="n"/>
       <c r="K47" s="211" t="n"/>
       <c r="L47" s="210" t="n"/>
-      <c r="M47" s="211" t="n"/>
+      <c r="M47" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N47" s="211" t="n"/>
-      <c r="O47" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O47" s="211" t="n"/>
       <c r="P47" s="211" t="n"/>
       <c r="Q47" s="233" t="n"/>
       <c r="R47" s="212" t="n"/>
@@ -7128,13 +7128,13 @@
       </c>
       <c r="J48" s="211" t="n"/>
       <c r="K48" s="211" t="n"/>
-      <c r="L48" s="210" t="n"/>
+      <c r="L48" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M48" s="211" t="n"/>
-      <c r="N48" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N48" s="211" t="n"/>
       <c r="O48" s="211" t="n"/>
       <c r="P48" s="211" t="n"/>
       <c r="Q48" s="233" t="n"/>
@@ -7198,19 +7198,19 @@
         </is>
       </c>
       <c r="J49" s="211" t="n"/>
-      <c r="K49" s="211" t="n"/>
-      <c r="L49" s="210" t="inlineStr">
+      <c r="K49" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M49" s="211" t="n"/>
+      <c r="L49" s="210" t="n"/>
+      <c r="M49" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N49" s="211" t="n"/>
-      <c r="O49" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O49" s="211" t="n"/>
       <c r="P49" s="211" t="n"/>
       <c r="Q49" s="233" t="n"/>
       <c r="R49" s="212" t="n"/>
@@ -7274,13 +7274,13 @@
       </c>
       <c r="J50" s="211" t="n"/>
       <c r="K50" s="211" t="n"/>
-      <c r="L50" s="210" t="n"/>
+      <c r="L50" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M50" s="211" t="n"/>
-      <c r="N50" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N50" s="211" t="n"/>
       <c r="O50" s="211" t="n"/>
       <c r="P50" s="211" t="n"/>
       <c r="Q50" s="233" t="n"/>
@@ -7340,19 +7340,19 @@
         </is>
       </c>
       <c r="J51" s="211" t="n"/>
-      <c r="K51" s="211" t="n"/>
-      <c r="L51" s="210" t="inlineStr">
+      <c r="K51" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M51" s="211" t="n"/>
+      <c r="L51" s="210" t="n"/>
+      <c r="M51" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N51" s="211" t="n"/>
-      <c r="O51" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O51" s="211" t="n"/>
       <c r="P51" s="211" t="n"/>
       <c r="Q51" s="233" t="n"/>
       <c r="R51" s="212" t="n"/>
@@ -7417,13 +7417,13 @@
       <c r="J52" s="211" t="n"/>
       <c r="K52" s="211" t="n"/>
       <c r="L52" s="210" t="n"/>
-      <c r="M52" s="211" t="n"/>
+      <c r="M52" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N52" s="211" t="n"/>
-      <c r="O52" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O52" s="211" t="n"/>
       <c r="P52" s="211" t="n"/>
       <c r="Q52" s="233" t="n"/>
       <c r="R52" s="212" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="I53" s="211" t="n"/>
       <c r="J53" s="211" t="n"/>
-      <c r="K53" s="211" t="n"/>
-      <c r="L53" s="210" t="inlineStr">
+      <c r="K53" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L53" s="210" t="n"/>
       <c r="M53" s="211" t="n"/>
       <c r="N53" s="211" t="n"/>
       <c r="O53" s="211" t="n"/>
@@ -7554,13 +7554,13 @@
       </c>
       <c r="J54" s="211" t="n"/>
       <c r="K54" s="211" t="n"/>
-      <c r="L54" s="210" t="n"/>
+      <c r="L54" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M54" s="211" t="n"/>
-      <c r="N54" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N54" s="211" t="n"/>
       <c r="O54" s="211" t="n"/>
       <c r="P54" s="211" t="n"/>
       <c r="Q54" s="233" t="n"/>
@@ -7613,13 +7613,13 @@
       <c r="I55" s="211" t="n"/>
       <c r="J55" s="211" t="n"/>
       <c r="K55" s="211" t="n"/>
-      <c r="L55" s="210" t="n"/>
+      <c r="L55" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M55" s="211" t="n"/>
-      <c r="N55" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N55" s="211" t="n"/>
       <c r="O55" s="211" t="n"/>
       <c r="P55" s="211" t="n"/>
       <c r="Q55" s="233" t="n"/>
@@ -7675,20 +7675,20 @@
       </c>
       <c r="I56" s="211" t="n"/>
       <c r="J56" s="211" t="n"/>
-      <c r="K56" s="211" t="inlineStr">
+      <c r="K56" s="211" t="n"/>
+      <c r="L56" s="210" t="n"/>
+      <c r="M56" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N56" s="211" t="n"/>
+      <c r="O56" s="211" t="n"/>
+      <c r="P56" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L56" s="210" t="n"/>
-      <c r="M56" s="211" t="n"/>
-      <c r="N56" s="211" t="n"/>
-      <c r="O56" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P56" s="211" t="n"/>
       <c r="Q56" s="233" t="n"/>
       <c r="R56" s="212" t="n"/>
       <c r="S56" s="233" t="n"/>
@@ -7750,19 +7750,19 @@
         </is>
       </c>
       <c r="J57" s="211" t="n"/>
-      <c r="K57" s="211" t="n"/>
-      <c r="L57" s="210" t="inlineStr">
+      <c r="K57" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M57" s="211" t="n"/>
+      <c r="L57" s="210" t="n"/>
+      <c r="M57" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N57" s="211" t="n"/>
-      <c r="O57" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O57" s="211" t="n"/>
       <c r="P57" s="211" t="n"/>
       <c r="Q57" s="233" t="n"/>
       <c r="R57" s="212" t="n"/>
@@ -7827,18 +7827,18 @@
       <c r="J58" s="211" t="n"/>
       <c r="K58" s="211" t="inlineStr">
         <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="L58" s="210" t="inlineStr">
-        <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L58" s="210" t="n"/>
       <c r="M58" s="211" t="n"/>
       <c r="N58" s="211" t="n"/>
       <c r="O58" s="211" t="n"/>
-      <c r="P58" s="211" t="n"/>
+      <c r="P58" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
       <c r="Q58" s="233" t="n"/>
       <c r="R58" s="212" t="n"/>
       <c r="S58" s="233" t="n"/>
@@ -7907,19 +7907,19 @@
         </is>
       </c>
       <c r="J59" s="211" t="n"/>
-      <c r="K59" s="211" t="n"/>
-      <c r="L59" s="210" t="inlineStr">
+      <c r="K59" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M59" s="211" t="n"/>
+      <c r="L59" s="210" t="n"/>
+      <c r="M59" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N59" s="211" t="n"/>
-      <c r="O59" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O59" s="211" t="n"/>
       <c r="P59" s="211" t="n"/>
       <c r="Q59" s="233" t="n"/>
       <c r="R59" s="212" t="n"/>
@@ -7991,13 +7991,13 @@
       <c r="J60" s="211" t="n"/>
       <c r="K60" s="211" t="n"/>
       <c r="L60" s="210" t="n"/>
-      <c r="M60" s="211" t="n"/>
+      <c r="M60" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N60" s="211" t="n"/>
-      <c r="O60" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O60" s="211" t="n"/>
       <c r="P60" s="211" t="n"/>
       <c r="Q60" s="233" t="n"/>
       <c r="R60" s="212" t="n"/>
@@ -8063,20 +8063,20 @@
       </c>
       <c r="I61" s="211" t="n"/>
       <c r="J61" s="211" t="n"/>
-      <c r="K61" s="211" t="inlineStr">
+      <c r="K61" s="211" t="n"/>
+      <c r="L61" s="210" t="n"/>
+      <c r="M61" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N61" s="211" t="n"/>
+      <c r="O61" s="211" t="n"/>
+      <c r="P61" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L61" s="210" t="n"/>
-      <c r="M61" s="211" t="n"/>
-      <c r="N61" s="211" t="n"/>
-      <c r="O61" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P61" s="211" t="n"/>
       <c r="Q61" s="233" t="n"/>
       <c r="R61" s="212" t="n"/>
       <c r="S61" s="233" t="n"/>
@@ -8143,13 +8143,13 @@
       <c r="J62" s="211" t="n"/>
       <c r="K62" s="211" t="n"/>
       <c r="L62" s="210" t="n"/>
-      <c r="M62" s="211" t="n"/>
+      <c r="M62" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N62" s="211" t="n"/>
-      <c r="O62" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O62" s="211" t="n"/>
       <c r="P62" s="211" t="n"/>
       <c r="Q62" s="233" t="n"/>
       <c r="R62" s="212" t="n"/>
@@ -8207,12 +8207,12 @@
       <c r="H63" s="211" t="n"/>
       <c r="I63" s="211" t="n"/>
       <c r="J63" s="211" t="n"/>
-      <c r="K63" s="211" t="n"/>
-      <c r="L63" s="210" t="inlineStr">
+      <c r="K63" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L63" s="210" t="n"/>
       <c r="M63" s="211" t="n"/>
       <c r="N63" s="211" t="n"/>
       <c r="O63" s="211" t="n"/>
@@ -8289,28 +8289,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K64" s="211" t="n"/>
+      <c r="K64" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L64" s="210" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M64" s="211" t="n"/>
+      <c r="M64" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N64" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O64" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P64" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O64" s="211" t="n"/>
+      <c r="P64" s="211" t="n"/>
       <c r="Q64" s="233" t="n"/>
       <c r="R64" s="212" t="n"/>
       <c r="S64" s="233" t="n"/>
@@ -8457,12 +8457,12 @@
       </c>
       <c r="I66" s="211" t="n"/>
       <c r="J66" s="211" t="n"/>
-      <c r="K66" s="211" t="n"/>
-      <c r="L66" s="210" t="inlineStr">
+      <c r="K66" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L66" s="210" t="n"/>
       <c r="M66" s="211" t="n"/>
       <c r="N66" s="211" t="n"/>
       <c r="O66" s="211" t="n"/>
@@ -8528,13 +8528,13 @@
       <c r="I67" s="211" t="n"/>
       <c r="J67" s="211" t="n"/>
       <c r="K67" s="211" t="n"/>
-      <c r="L67" s="210" t="n"/>
+      <c r="L67" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M67" s="211" t="n"/>
-      <c r="N67" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N67" s="211" t="n"/>
       <c r="O67" s="211" t="n"/>
       <c r="P67" s="211" t="n"/>
       <c r="Q67" s="233" t="n"/>
@@ -8590,12 +8590,12 @@
       <c r="H68" s="211" t="n"/>
       <c r="I68" s="211" t="n"/>
       <c r="J68" s="211" t="n"/>
-      <c r="K68" s="211" t="n"/>
-      <c r="L68" s="210" t="inlineStr">
+      <c r="K68" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L68" s="210" t="n"/>
       <c r="M68" s="211" t="n"/>
       <c r="N68" s="211" t="n"/>
       <c r="O68" s="211" t="n"/>
@@ -8653,20 +8653,20 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K69" s="211" t="inlineStr">
+      <c r="K69" s="211" t="n"/>
+      <c r="L69" s="210" t="n"/>
+      <c r="M69" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N69" s="211" t="n"/>
+      <c r="O69" s="211" t="n"/>
+      <c r="P69" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L69" s="210" t="n"/>
-      <c r="M69" s="211" t="n"/>
-      <c r="N69" s="211" t="n"/>
-      <c r="O69" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P69" s="211" t="n"/>
       <c r="Q69" s="233" t="n"/>
       <c r="R69" s="212" t="n"/>
       <c r="S69" s="233" t="n"/>
@@ -8728,20 +8728,20 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K70" s="211" t="inlineStr">
+      <c r="K70" s="211" t="n"/>
+      <c r="L70" s="210" t="n"/>
+      <c r="M70" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N70" s="211" t="n"/>
+      <c r="O70" s="211" t="n"/>
+      <c r="P70" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L70" s="210" t="n"/>
-      <c r="M70" s="211" t="n"/>
-      <c r="N70" s="211" t="n"/>
-      <c r="O70" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P70" s="211" t="n"/>
       <c r="Q70" s="233" t="n"/>
       <c r="R70" s="212" t="n"/>
       <c r="S70" s="233" t="n"/>
@@ -8803,20 +8803,20 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K71" s="211" t="inlineStr">
+      <c r="K71" s="211" t="n"/>
+      <c r="L71" s="210" t="n"/>
+      <c r="M71" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N71" s="211" t="n"/>
+      <c r="O71" s="211" t="n"/>
+      <c r="P71" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L71" s="210" t="n"/>
-      <c r="M71" s="211" t="n"/>
-      <c r="N71" s="211" t="n"/>
-      <c r="O71" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P71" s="211" t="n"/>
       <c r="Q71" s="233" t="n"/>
       <c r="R71" s="212" t="inlineStr">
         <is>
@@ -8884,13 +8884,13 @@
       </c>
       <c r="K72" s="211" t="n"/>
       <c r="L72" s="210" t="n"/>
-      <c r="M72" s="211" t="n"/>
+      <c r="M72" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N72" s="211" t="n"/>
-      <c r="O72" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O72" s="211" t="n"/>
       <c r="P72" s="211" t="n"/>
       <c r="Q72" s="233" t="n"/>
       <c r="R72" s="212" t="inlineStr">
@@ -8963,13 +8963,13 @@
       </c>
       <c r="K73" s="211" t="n"/>
       <c r="L73" s="210" t="n"/>
-      <c r="M73" s="211" t="n"/>
+      <c r="M73" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N73" s="211" t="n"/>
-      <c r="O73" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O73" s="211" t="n"/>
       <c r="P73" s="211" t="n"/>
       <c r="Q73" s="233" t="n"/>
       <c r="R73" s="212" t="n"/>
@@ -9038,13 +9038,13 @@
       </c>
       <c r="K74" s="211" t="n"/>
       <c r="L74" s="210" t="n"/>
-      <c r="M74" s="211" t="n"/>
+      <c r="M74" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N74" s="211" t="n"/>
-      <c r="O74" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O74" s="211" t="n"/>
       <c r="P74" s="211" t="n"/>
       <c r="Q74" s="233" t="n"/>
       <c r="R74" s="212" t="n"/>
@@ -9102,13 +9102,13 @@
       <c r="K75" s="211" t="n"/>
       <c r="L75" s="210" t="n"/>
       <c r="M75" s="211" t="n"/>
-      <c r="N75" s="211" t="n"/>
+      <c r="N75" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="O75" s="211" t="n"/>
-      <c r="P75" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="P75" s="211" t="n"/>
       <c r="Q75" s="233" t="n"/>
       <c r="R75" s="212" t="inlineStr">
         <is>
@@ -9172,13 +9172,13 @@
       </c>
       <c r="K76" s="211" t="n"/>
       <c r="L76" s="210" t="n"/>
-      <c r="M76" s="211" t="n"/>
+      <c r="M76" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N76" s="211" t="n"/>
-      <c r="O76" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O76" s="211" t="n"/>
       <c r="P76" s="211" t="n"/>
       <c r="Q76" s="233" t="n"/>
       <c r="R76" s="212" t="inlineStr">
@@ -9255,28 +9255,28 @@
       </c>
       <c r="K77" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L77" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M77" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N77" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O77" s="211" t="n"/>
+      <c r="P77" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L77" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M77" s="211" t="n"/>
-      <c r="N77" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O77" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P77" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
         </is>
       </c>
       <c r="Q77" s="233" t="n"/>
@@ -9352,19 +9352,19 @@
         </is>
       </c>
       <c r="J78" s="211" t="n"/>
-      <c r="K78" s="211" t="n"/>
-      <c r="L78" s="210" t="inlineStr">
+      <c r="K78" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M78" s="211" t="n"/>
+      <c r="L78" s="210" t="n"/>
+      <c r="M78" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N78" s="211" t="n"/>
-      <c r="O78" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O78" s="211" t="n"/>
       <c r="P78" s="211" t="n"/>
       <c r="Q78" s="233" t="n"/>
       <c r="R78" s="212" t="n"/>
@@ -9435,28 +9435,28 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K79" s="211" t="n"/>
+      <c r="K79" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L79" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M79" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M79" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N79" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O79" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P79" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O79" s="211" t="n"/>
+      <c r="P79" s="211" t="n"/>
       <c r="Q79" s="233" t="n"/>
       <c r="R79" s="212" t="n"/>
       <c r="S79" s="233" t="n"/>
@@ -9538,19 +9538,19 @@
         </is>
       </c>
       <c r="J80" s="211" t="n"/>
-      <c r="K80" s="211" t="n"/>
-      <c r="L80" s="210" t="inlineStr">
+      <c r="K80" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M80" s="211" t="n"/>
+      <c r="L80" s="210" t="n"/>
+      <c r="M80" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N80" s="211" t="n"/>
-      <c r="O80" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O80" s="211" t="n"/>
       <c r="P80" s="211" t="n"/>
       <c r="Q80" s="233" t="n"/>
       <c r="R80" s="212" t="n"/>
@@ -9621,28 +9621,28 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K81" s="211" t="n"/>
+      <c r="K81" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L81" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M81" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M81" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N81" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O81" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P81" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O81" s="211" t="n"/>
+      <c r="P81" s="211" t="n"/>
       <c r="Q81" s="233" t="n"/>
       <c r="R81" s="212" t="n"/>
       <c r="S81" s="233" t="n"/>
@@ -9722,13 +9722,13 @@
       <c r="J82" s="211" t="n"/>
       <c r="K82" s="211" t="n"/>
       <c r="L82" s="210" t="n"/>
-      <c r="M82" s="211" t="n"/>
+      <c r="M82" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N82" s="211" t="n"/>
-      <c r="O82" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O82" s="211" t="n"/>
       <c r="P82" s="211" t="n"/>
       <c r="Q82" s="233" t="n"/>
       <c r="R82" s="212" t="n"/>
@@ -9797,22 +9797,22 @@
       <c r="J83" s="211" t="n"/>
       <c r="K83" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L83" s="210" t="n"/>
+      <c r="M83" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N83" s="211" t="n"/>
+      <c r="O83" s="211" t="n"/>
+      <c r="P83" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L83" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M83" s="211" t="n"/>
-      <c r="N83" s="211" t="n"/>
-      <c r="O83" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P83" s="211" t="n"/>
       <c r="Q83" s="233" t="n"/>
       <c r="R83" s="212" t="n"/>
       <c r="S83" s="233" t="n"/>
@@ -9882,28 +9882,28 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K84" s="211" t="n"/>
+      <c r="K84" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L84" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M84" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M84" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N84" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O84" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P84" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O84" s="211" t="n"/>
+      <c r="P84" s="211" t="n"/>
       <c r="Q84" s="233" t="n"/>
       <c r="R84" s="212" t="n"/>
       <c r="S84" s="233" t="n"/>
@@ -9987,26 +9987,26 @@
       </c>
       <c r="K85" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L85" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M85" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N85" s="211" t="n"/>
+      <c r="O85" s="211" t="n"/>
+      <c r="P85" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L85" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M85" s="211" t="n"/>
-      <c r="N85" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O85" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P85" s="211" t="n"/>
       <c r="Q85" s="233" t="n"/>
       <c r="R85" s="212" t="n"/>
       <c r="S85" s="233" t="n"/>
@@ -10085,18 +10085,18 @@
         </is>
       </c>
       <c r="K86" s="211" t="n"/>
-      <c r="L86" s="210" t="n"/>
-      <c r="M86" s="211" t="n"/>
-      <c r="N86" s="211" t="inlineStr">
+      <c r="L86" s="210" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="O86" s="211" t="inlineStr">
+      <c r="M86" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="N86" s="211" t="n"/>
+      <c r="O86" s="211" t="n"/>
       <c r="P86" s="211" t="n"/>
       <c r="Q86" s="233" t="n"/>
       <c r="R86" s="212" t="n"/>
@@ -10167,23 +10167,23 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K87" s="211" t="n"/>
+      <c r="K87" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L87" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M87" s="211" t="n"/>
-      <c r="N87" s="211" t="inlineStr">
-        <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="O87" s="211" t="inlineStr">
+      <c r="M87" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="N87" s="211" t="n"/>
+      <c r="O87" s="211" t="n"/>
       <c r="P87" s="211" t="n"/>
       <c r="Q87" s="233" t="n"/>
       <c r="R87" s="212" t="n"/>
@@ -10264,26 +10264,26 @@
       </c>
       <c r="K88" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L88" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M88" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N88" s="211" t="n"/>
+      <c r="O88" s="211" t="n"/>
+      <c r="P88" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L88" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M88" s="211" t="n"/>
-      <c r="N88" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O88" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P88" s="211" t="n"/>
       <c r="Q88" s="233" t="n"/>
       <c r="R88" s="212" t="n"/>
       <c r="S88" s="233" t="n"/>
@@ -10355,22 +10355,22 @@
       <c r="J89" s="211" t="n"/>
       <c r="K89" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L89" s="210" t="n"/>
+      <c r="M89" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N89" s="211" t="n"/>
+      <c r="O89" s="211" t="n"/>
+      <c r="P89" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L89" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M89" s="211" t="n"/>
-      <c r="N89" s="211" t="n"/>
-      <c r="O89" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P89" s="211" t="n"/>
       <c r="Q89" s="233" t="n"/>
       <c r="R89" s="212" t="n"/>
       <c r="S89" s="233" t="n"/>
@@ -10434,13 +10434,13 @@
       </c>
       <c r="K90" s="211" t="n"/>
       <c r="L90" s="210" t="n"/>
-      <c r="M90" s="211" t="n"/>
+      <c r="M90" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N90" s="211" t="n"/>
-      <c r="O90" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O90" s="211" t="n"/>
       <c r="P90" s="211" t="n"/>
       <c r="Q90" s="233" t="n"/>
       <c r="R90" s="212" t="inlineStr">
@@ -10509,13 +10509,13 @@
       </c>
       <c r="K91" s="211" t="n"/>
       <c r="L91" s="210" t="n"/>
-      <c r="M91" s="211" t="n"/>
+      <c r="M91" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N91" s="211" t="n"/>
-      <c r="O91" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O91" s="211" t="n"/>
       <c r="P91" s="211" t="n"/>
       <c r="Q91" s="233" t="n"/>
       <c r="R91" s="212" t="n"/>
@@ -10575,13 +10575,13 @@
       </c>
       <c r="J92" s="211" t="n"/>
       <c r="K92" s="211" t="n"/>
-      <c r="L92" s="210" t="n"/>
+      <c r="L92" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M92" s="211" t="n"/>
-      <c r="N92" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N92" s="211" t="n"/>
       <c r="O92" s="211" t="n"/>
       <c r="P92" s="211" t="n"/>
       <c r="Q92" s="233" t="n"/>
@@ -10638,13 +10638,13 @@
       </c>
       <c r="J93" s="211" t="n"/>
       <c r="K93" s="211" t="n"/>
-      <c r="L93" s="210" t="n"/>
+      <c r="L93" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M93" s="211" t="n"/>
-      <c r="N93" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N93" s="211" t="n"/>
       <c r="O93" s="211" t="n"/>
       <c r="P93" s="211" t="n"/>
       <c r="Q93" s="233" t="n"/>
@@ -10702,13 +10702,13 @@
       </c>
       <c r="K94" s="211" t="n"/>
       <c r="L94" s="210" t="n"/>
-      <c r="M94" s="211" t="n"/>
+      <c r="M94" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N94" s="211" t="n"/>
-      <c r="O94" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O94" s="211" t="n"/>
       <c r="P94" s="211" t="n"/>
       <c r="Q94" s="233" t="n"/>
       <c r="R94" s="212" t="n"/>
@@ -10772,13 +10772,13 @@
       <c r="I95" s="211" t="n"/>
       <c r="J95" s="211" t="n"/>
       <c r="K95" s="211" t="n"/>
-      <c r="L95" s="210" t="n"/>
+      <c r="L95" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M95" s="211" t="n"/>
-      <c r="N95" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N95" s="211" t="n"/>
       <c r="O95" s="211" t="n"/>
       <c r="P95" s="211" t="n"/>
       <c r="Q95" s="233" t="n"/>
@@ -10836,13 +10836,13 @@
       <c r="J96" s="211" t="n"/>
       <c r="K96" s="211" t="n"/>
       <c r="L96" s="210" t="n"/>
-      <c r="M96" s="211" t="n"/>
+      <c r="M96" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N96" s="211" t="n"/>
-      <c r="O96" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O96" s="211" t="n"/>
       <c r="P96" s="211" t="n"/>
       <c r="Q96" s="233" t="n"/>
       <c r="R96" s="212" t="n"/>
@@ -10897,19 +10897,19 @@
         </is>
       </c>
       <c r="J97" s="211" t="n"/>
-      <c r="K97" s="211" t="n"/>
-      <c r="L97" s="210" t="inlineStr">
+      <c r="K97" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M97" s="211" t="n"/>
+      <c r="L97" s="210" t="n"/>
+      <c r="M97" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N97" s="211" t="n"/>
-      <c r="O97" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O97" s="211" t="n"/>
       <c r="P97" s="211" t="n"/>
       <c r="Q97" s="233" t="n"/>
       <c r="R97" s="212" t="n"/>
@@ -10984,28 +10984,28 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K98" s="211" t="n"/>
+      <c r="K98" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L98" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M98" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M98" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N98" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O98" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P98" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O98" s="211" t="n"/>
+      <c r="P98" s="211" t="n"/>
       <c r="Q98" s="233" t="n"/>
       <c r="R98" s="212" t="n"/>
       <c r="S98" s="233" t="n"/>
@@ -11080,13 +11080,13 @@
       <c r="I99" s="211" t="n"/>
       <c r="J99" s="211" t="n"/>
       <c r="K99" s="211" t="n"/>
-      <c r="L99" s="210" t="n"/>
+      <c r="L99" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M99" s="211" t="n"/>
-      <c r="N99" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N99" s="211" t="n"/>
       <c r="O99" s="211" t="n"/>
       <c r="P99" s="211" t="n"/>
       <c r="Q99" s="233" t="n"/>
@@ -11147,13 +11147,13 @@
       </c>
       <c r="J100" s="211" t="n"/>
       <c r="K100" s="211" t="n"/>
-      <c r="L100" s="210" t="n"/>
+      <c r="L100" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M100" s="211" t="n"/>
-      <c r="N100" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N100" s="211" t="n"/>
       <c r="O100" s="211" t="n"/>
       <c r="P100" s="211" t="n"/>
       <c r="Q100" s="233" t="n"/>
@@ -11264,20 +11264,20 @@
         </is>
       </c>
       <c r="J101" s="211" t="n"/>
-      <c r="K101" s="211" t="inlineStr">
+      <c r="K101" s="211" t="n"/>
+      <c r="L101" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M101" s="211" t="n"/>
+      <c r="N101" s="211" t="n"/>
+      <c r="O101" s="211" t="n"/>
+      <c r="P101" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L101" s="210" t="n"/>
-      <c r="M101" s="211" t="n"/>
-      <c r="N101" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O101" s="211" t="n"/>
-      <c r="P101" s="211" t="n"/>
       <c r="Q101" s="233" t="n"/>
       <c r="R101" s="212" t="inlineStr">
         <is>
@@ -11374,13 +11374,13 @@
       </c>
       <c r="J102" s="211" t="n"/>
       <c r="K102" s="211" t="n"/>
-      <c r="L102" s="210" t="n"/>
+      <c r="L102" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M102" s="211" t="n"/>
-      <c r="N102" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N102" s="211" t="n"/>
       <c r="O102" s="211" t="n"/>
       <c r="P102" s="211" t="n"/>
       <c r="Q102" s="233" t="n"/>
@@ -11476,13 +11476,13 @@
       <c r="J103" s="211" t="n"/>
       <c r="K103" s="211" t="n"/>
       <c r="L103" s="210" t="n"/>
-      <c r="M103" s="211" t="n"/>
+      <c r="M103" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N103" s="211" t="n"/>
-      <c r="O103" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O103" s="211" t="n"/>
       <c r="P103" s="211" t="n"/>
       <c r="Q103" s="233" t="n"/>
       <c r="R103" s="212" t="n"/>
@@ -11580,13 +11580,13 @@
       </c>
       <c r="J104" s="211" t="n"/>
       <c r="K104" s="211" t="n"/>
-      <c r="L104" s="210" t="n"/>
+      <c r="L104" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M104" s="211" t="n"/>
-      <c r="N104" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N104" s="211" t="n"/>
       <c r="O104" s="211" t="n"/>
       <c r="P104" s="211" t="n"/>
       <c r="Q104" s="233" t="n"/>
@@ -11688,28 +11688,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K105" s="211" t="n"/>
+      <c r="K105" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L105" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M105" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M105" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N105" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O105" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P105" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O105" s="211" t="n"/>
+      <c r="P105" s="211" t="n"/>
       <c r="Q105" s="233" t="n"/>
       <c r="R105" s="212" t="n"/>
       <c r="S105" s="233" t="n"/>
@@ -11829,28 +11829,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K106" s="211" t="n"/>
+      <c r="K106" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L106" s="210" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M106" s="211" t="n"/>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M106" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N106" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O106" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P106" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O106" s="211" t="n"/>
+      <c r="P106" s="211" t="n"/>
       <c r="Q106" s="233" t="n"/>
       <c r="R106" s="212" t="n"/>
       <c r="S106" s="233" t="n"/>
@@ -11963,13 +11963,13 @@
       </c>
       <c r="J107" s="211" t="n"/>
       <c r="K107" s="211" t="n"/>
-      <c r="L107" s="210" t="n"/>
+      <c r="L107" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M107" s="211" t="n"/>
-      <c r="N107" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N107" s="211" t="n"/>
       <c r="O107" s="211" t="n"/>
       <c r="P107" s="211" t="n"/>
       <c r="Q107" s="233" t="n"/>
@@ -12067,20 +12067,20 @@
         </is>
       </c>
       <c r="J108" s="211" t="n"/>
-      <c r="K108" s="211" t="inlineStr">
+      <c r="K108" s="211" t="n"/>
+      <c r="L108" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M108" s="211" t="n"/>
+      <c r="N108" s="211" t="n"/>
+      <c r="O108" s="211" t="n"/>
+      <c r="P108" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L108" s="210" t="n"/>
-      <c r="M108" s="211" t="n"/>
-      <c r="N108" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O108" s="211" t="n"/>
-      <c r="P108" s="211" t="n"/>
       <c r="Q108" s="233" t="n"/>
       <c r="R108" s="212" t="n"/>
       <c r="S108" s="233" t="n"/>
@@ -12177,13 +12177,13 @@
       </c>
       <c r="J109" s="211" t="n"/>
       <c r="K109" s="211" t="n"/>
-      <c r="L109" s="210" t="n"/>
+      <c r="L109" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M109" s="211" t="n"/>
-      <c r="N109" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N109" s="211" t="n"/>
       <c r="O109" s="211" t="n"/>
       <c r="P109" s="211" t="n"/>
       <c r="Q109" s="233" t="n"/>
@@ -12257,28 +12257,28 @@
       </c>
       <c r="K110" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L110" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M110" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N110" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O110" s="211" t="n"/>
+      <c r="P110" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L110" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M110" s="211" t="n"/>
-      <c r="N110" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O110" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P110" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
         </is>
       </c>
       <c r="Q110" s="233" t="n"/>
@@ -12368,26 +12368,26 @@
       </c>
       <c r="K111" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L111" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M111" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N111" s="211" t="n"/>
+      <c r="O111" s="211" t="n"/>
+      <c r="P111" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L111" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M111" s="211" t="n"/>
-      <c r="N111" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O111" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P111" s="211" t="n"/>
       <c r="Q111" s="233" t="n"/>
       <c r="R111" s="212" t="n"/>
       <c r="S111" s="233" t="n"/>
@@ -12471,26 +12471,26 @@
       </c>
       <c r="K112" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L112" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M112" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N112" s="211" t="n"/>
+      <c r="O112" s="211" t="n"/>
+      <c r="P112" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L112" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M112" s="211" t="n"/>
-      <c r="N112" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O112" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P112" s="211" t="n"/>
       <c r="Q112" s="233" t="n"/>
       <c r="R112" s="212" t="n"/>
       <c r="S112" s="233" t="n"/>
@@ -12562,13 +12562,13 @@
       </c>
       <c r="K113" s="211" t="n"/>
       <c r="L113" s="210" t="n"/>
-      <c r="M113" s="211" t="n"/>
+      <c r="M113" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N113" s="211" t="n"/>
-      <c r="O113" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O113" s="211" t="n"/>
       <c r="P113" s="211" t="n"/>
       <c r="Q113" s="233" t="n"/>
       <c r="R113" s="212" t="n"/>
@@ -12625,18 +12625,18 @@
       <c r="J114" s="211" t="n"/>
       <c r="K114" s="211" t="inlineStr">
         <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="L114" s="210" t="inlineStr">
-        <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L114" s="210" t="n"/>
       <c r="M114" s="211" t="n"/>
       <c r="N114" s="211" t="n"/>
       <c r="O114" s="211" t="n"/>
-      <c r="P114" s="211" t="n"/>
+      <c r="P114" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
       <c r="Q114" s="233" t="n"/>
       <c r="R114" s="212" t="n"/>
       <c r="S114" s="233" t="n"/>
@@ -12698,17 +12698,17 @@
       <c r="L115" s="210" t="n"/>
       <c r="M115" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N115" s="211" t="n"/>
+      <c r="O115" s="211" t="n"/>
+      <c r="P115" s="211" t="n"/>
+      <c r="Q115" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N115" s="211" t="n"/>
-      <c r="O115" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P115" s="211" t="n"/>
-      <c r="Q115" s="233" t="n"/>
       <c r="R115" s="212" t="n"/>
       <c r="S115" s="233" t="n"/>
       <c r="T115" s="218" t="n"/>
@@ -12767,13 +12767,13 @@
       <c r="J116" s="211" t="n"/>
       <c r="K116" s="211" t="n"/>
       <c r="L116" s="210" t="n"/>
-      <c r="M116" s="211" t="n"/>
+      <c r="M116" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N116" s="211" t="n"/>
-      <c r="O116" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O116" s="211" t="n"/>
       <c r="P116" s="211" t="n"/>
       <c r="Q116" s="233" t="n"/>
       <c r="R116" s="212" t="n"/>
@@ -12838,26 +12838,26 @@
       </c>
       <c r="K117" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L117" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M117" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N117" s="211" t="n"/>
+      <c r="O117" s="211" t="n"/>
+      <c r="P117" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L117" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M117" s="211" t="n"/>
-      <c r="N117" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O117" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P117" s="211" t="n"/>
       <c r="Q117" s="233" t="n"/>
       <c r="R117" s="212" t="n"/>
       <c r="S117" s="233" t="n"/>
@@ -12933,22 +12933,22 @@
       <c r="J118" s="211" t="n"/>
       <c r="K118" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L118" s="210" t="n"/>
+      <c r="M118" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N118" s="211" t="n"/>
+      <c r="O118" s="211" t="n"/>
+      <c r="P118" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L118" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M118" s="211" t="n"/>
-      <c r="N118" s="211" t="n"/>
-      <c r="O118" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P118" s="211" t="n"/>
       <c r="Q118" s="233" t="n"/>
       <c r="R118" s="212" t="n"/>
       <c r="S118" s="233" t="n"/>
@@ -13014,19 +13014,19 @@
         </is>
       </c>
       <c r="J119" s="211" t="n"/>
-      <c r="K119" s="211" t="n"/>
-      <c r="L119" s="210" t="inlineStr">
+      <c r="K119" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M119" s="211" t="n"/>
+      <c r="L119" s="210" t="n"/>
+      <c r="M119" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N119" s="211" t="n"/>
-      <c r="O119" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O119" s="211" t="n"/>
       <c r="P119" s="211" t="n"/>
       <c r="Q119" s="233" t="n"/>
       <c r="R119" s="212" t="n"/>
@@ -13099,13 +13099,13 @@
       </c>
       <c r="K120" s="211" t="n"/>
       <c r="L120" s="210" t="n"/>
-      <c r="M120" s="211" t="n"/>
+      <c r="M120" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N120" s="211" t="n"/>
-      <c r="O120" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O120" s="211" t="n"/>
       <c r="P120" s="211" t="n"/>
       <c r="Q120" s="233" t="n"/>
       <c r="R120" s="212" t="n"/>
@@ -13166,13 +13166,13 @@
       </c>
       <c r="K121" s="211" t="n"/>
       <c r="L121" s="210" t="n"/>
-      <c r="M121" s="211" t="n"/>
+      <c r="M121" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N121" s="211" t="n"/>
-      <c r="O121" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O121" s="211" t="n"/>
       <c r="P121" s="211" t="n"/>
       <c r="Q121" s="233" t="n"/>
       <c r="R121" s="212" t="n"/>
@@ -13233,13 +13233,13 @@
       </c>
       <c r="K122" s="211" t="n"/>
       <c r="L122" s="210" t="n"/>
-      <c r="M122" s="211" t="n"/>
+      <c r="M122" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N122" s="211" t="n"/>
-      <c r="O122" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O122" s="211" t="n"/>
       <c r="P122" s="211" t="n"/>
       <c r="Q122" s="233" t="n"/>
       <c r="R122" s="212" t="n"/>
@@ -13304,22 +13304,22 @@
       <c r="J123" s="211" t="n"/>
       <c r="K123" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L123" s="210" t="n"/>
+      <c r="M123" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N123" s="211" t="n"/>
+      <c r="O123" s="211" t="n"/>
+      <c r="P123" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L123" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M123" s="211" t="n"/>
-      <c r="N123" s="211" t="n"/>
-      <c r="O123" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P123" s="211" t="n"/>
       <c r="Q123" s="233" t="n"/>
       <c r="R123" s="212" t="n"/>
       <c r="S123" s="233" t="n"/>
@@ -13382,13 +13382,13 @@
       </c>
       <c r="J124" s="211" t="n"/>
       <c r="K124" s="211" t="n"/>
-      <c r="L124" s="210" t="n"/>
+      <c r="L124" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M124" s="211" t="n"/>
-      <c r="N124" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N124" s="211" t="n"/>
       <c r="O124" s="211" t="n"/>
       <c r="P124" s="211" t="n"/>
       <c r="Q124" s="233" t="n"/>
@@ -13449,13 +13449,13 @@
       </c>
       <c r="J125" s="211" t="n"/>
       <c r="K125" s="211" t="n"/>
-      <c r="L125" s="210" t="n"/>
+      <c r="L125" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M125" s="211" t="n"/>
-      <c r="N125" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N125" s="211" t="n"/>
       <c r="O125" s="211" t="n"/>
       <c r="P125" s="211" t="n"/>
       <c r="Q125" s="233" t="n"/>
@@ -13516,13 +13516,13 @@
       </c>
       <c r="J126" s="211" t="n"/>
       <c r="K126" s="211" t="n"/>
-      <c r="L126" s="210" t="n"/>
+      <c r="L126" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M126" s="211" t="n"/>
-      <c r="N126" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N126" s="211" t="n"/>
       <c r="O126" s="211" t="n"/>
       <c r="P126" s="211" t="n"/>
       <c r="Q126" s="233" t="n"/>
@@ -13590,20 +13590,20 @@
         </is>
       </c>
       <c r="J127" s="211" t="n"/>
-      <c r="K127" s="211" t="inlineStr">
+      <c r="K127" s="211" t="n"/>
+      <c r="L127" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M127" s="211" t="n"/>
+      <c r="N127" s="211" t="n"/>
+      <c r="O127" s="211" t="n"/>
+      <c r="P127" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L127" s="210" t="n"/>
-      <c r="M127" s="211" t="n"/>
-      <c r="N127" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O127" s="211" t="n"/>
-      <c r="P127" s="211" t="n"/>
       <c r="Q127" s="233" t="n"/>
       <c r="R127" s="212" t="inlineStr">
         <is>
@@ -13677,7 +13677,11 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K128" s="211" t="n"/>
+      <c r="K128" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L128" s="210" t="inlineStr">
         <is>
           <t>N-</t>
@@ -13685,25 +13689,21 @@
       </c>
       <c r="M128" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N128" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
+      <c r="O128" s="211" t="n"/>
+      <c r="P128" s="211" t="n"/>
+      <c r="Q128" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N128" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O128" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P128" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
-      <c r="Q128" s="233" t="n"/>
       <c r="R128" s="212" t="n"/>
       <c r="S128" s="233" t="n"/>
       <c r="T128" s="218" t="n"/>
@@ -13777,13 +13777,13 @@
       </c>
       <c r="J129" s="211" t="n"/>
       <c r="K129" s="211" t="n"/>
-      <c r="L129" s="210" t="n"/>
+      <c r="L129" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M129" s="211" t="n"/>
-      <c r="N129" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N129" s="211" t="n"/>
       <c r="O129" s="211" t="n"/>
       <c r="P129" s="211" t="n"/>
       <c r="Q129" s="233" t="n"/>
@@ -13844,13 +13844,13 @@
       <c r="I130" s="211" t="n"/>
       <c r="J130" s="211" t="n"/>
       <c r="K130" s="211" t="n"/>
-      <c r="L130" s="210" t="n"/>
+      <c r="L130" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M130" s="211" t="n"/>
-      <c r="N130" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N130" s="211" t="n"/>
       <c r="O130" s="211" t="n"/>
       <c r="P130" s="211" t="n"/>
       <c r="Q130" s="233" t="n"/>
@@ -13903,13 +13903,13 @@
       <c r="I131" s="211" t="n"/>
       <c r="J131" s="211" t="n"/>
       <c r="K131" s="211" t="n"/>
-      <c r="L131" s="210" t="n"/>
+      <c r="L131" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M131" s="211" t="n"/>
-      <c r="N131" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N131" s="211" t="n"/>
       <c r="O131" s="211" t="n"/>
       <c r="P131" s="211" t="n"/>
       <c r="Q131" s="233" t="n"/>
@@ -13978,23 +13978,23 @@
         </is>
       </c>
       <c r="K132" s="211" t="n"/>
-      <c r="L132" s="210" t="n"/>
-      <c r="M132" s="211" t="n"/>
+      <c r="L132" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M132" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N132" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O132" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P132" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O132" s="211" t="n"/>
+      <c r="P132" s="211" t="n"/>
       <c r="Q132" s="233" t="n"/>
       <c r="R132" s="212" t="n"/>
       <c r="S132" s="233" t="n"/>
@@ -14065,13 +14065,13 @@
       </c>
       <c r="J133" s="211" t="n"/>
       <c r="K133" s="211" t="n"/>
-      <c r="L133" s="210" t="n"/>
+      <c r="L133" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M133" s="211" t="n"/>
-      <c r="N133" s="233" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N133" s="233" t="n"/>
       <c r="O133" s="211" t="n"/>
       <c r="P133" s="211" t="n"/>
       <c r="Q133" s="233" t="n"/>
@@ -14136,13 +14136,13 @@
       </c>
       <c r="J134" s="211" t="n"/>
       <c r="K134" s="211" t="n"/>
-      <c r="L134" s="210" t="n"/>
+      <c r="L134" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M134" s="211" t="n"/>
-      <c r="N134" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N134" s="211" t="n"/>
       <c r="O134" s="211" t="n"/>
       <c r="P134" s="211" t="n"/>
       <c r="Q134" s="233" t="n"/>
@@ -14203,13 +14203,13 @@
       </c>
       <c r="J135" s="211" t="n"/>
       <c r="K135" s="211" t="n"/>
-      <c r="L135" s="210" t="n"/>
+      <c r="L135" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M135" s="211" t="n"/>
-      <c r="N135" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N135" s="211" t="n"/>
       <c r="O135" s="211" t="n"/>
       <c r="P135" s="211" t="n"/>
       <c r="Q135" s="233" t="n"/>
@@ -14275,13 +14275,13 @@
       </c>
       <c r="K136" s="211" t="n"/>
       <c r="L136" s="210" t="n"/>
-      <c r="M136" s="211" t="n"/>
+      <c r="M136" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N136" s="211" t="n"/>
-      <c r="O136" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O136" s="211" t="n"/>
       <c r="P136" s="211" t="n"/>
       <c r="Q136" s="233" t="n"/>
       <c r="R136" s="212" t="n"/>
@@ -14384,13 +14384,13 @@
       </c>
       <c r="J137" s="211" t="n"/>
       <c r="K137" s="211" t="n"/>
-      <c r="L137" s="210" t="n"/>
+      <c r="L137" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M137" s="211" t="n"/>
-      <c r="N137" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N137" s="211" t="n"/>
       <c r="O137" s="211" t="n"/>
       <c r="P137" s="211" t="n"/>
       <c r="Q137" s="233" t="n"/>
@@ -14465,20 +14465,20 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K138" s="211" t="inlineStr">
+      <c r="K138" s="211" t="n"/>
+      <c r="L138" s="210" t="n"/>
+      <c r="M138" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N138" s="211" t="n"/>
+      <c r="O138" s="211" t="n"/>
+      <c r="P138" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L138" s="210" t="n"/>
-      <c r="M138" s="211" t="n"/>
-      <c r="N138" s="211" t="n"/>
-      <c r="O138" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P138" s="211" t="n"/>
       <c r="Q138" s="233" t="n"/>
       <c r="R138" s="212" t="n"/>
       <c r="S138" s="233" t="n"/>
@@ -14571,13 +14571,13 @@
       </c>
       <c r="J139" s="211" t="n"/>
       <c r="K139" s="211" t="n"/>
-      <c r="L139" s="210" t="n"/>
+      <c r="L139" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M139" s="211" t="n"/>
-      <c r="N139" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N139" s="211" t="n"/>
       <c r="O139" s="211" t="n"/>
       <c r="P139" s="211" t="n"/>
       <c r="Q139" s="233" t="n"/>
@@ -14654,22 +14654,22 @@
       <c r="J140" s="211" t="n"/>
       <c r="K140" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L140" s="210" t="n"/>
+      <c r="M140" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N140" s="211" t="n"/>
+      <c r="O140" s="211" t="n"/>
+      <c r="P140" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L140" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M140" s="211" t="n"/>
-      <c r="N140" s="211" t="n"/>
-      <c r="O140" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P140" s="211" t="n"/>
       <c r="Q140" s="233" t="n"/>
       <c r="R140" s="212" t="n"/>
       <c r="S140" s="233" t="n"/>
@@ -14765,20 +14765,20 @@
       </c>
       <c r="I141" s="211" t="n"/>
       <c r="J141" s="211" t="n"/>
-      <c r="K141" s="211" t="inlineStr">
+      <c r="K141" s="211" t="n"/>
+      <c r="L141" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M141" s="211" t="n"/>
+      <c r="N141" s="211" t="n"/>
+      <c r="O141" s="211" t="n"/>
+      <c r="P141" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L141" s="210" t="n"/>
-      <c r="M141" s="211" t="n"/>
-      <c r="N141" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O141" s="211" t="n"/>
-      <c r="P141" s="211" t="n"/>
       <c r="Q141" s="233" t="n"/>
       <c r="R141" s="212" t="n"/>
       <c r="S141" s="233" t="n"/>
@@ -14874,20 +14874,20 @@
         </is>
       </c>
       <c r="J142" s="211" t="n"/>
-      <c r="K142" s="211" t="inlineStr">
+      <c r="K142" s="211" t="n"/>
+      <c r="L142" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M142" s="211" t="n"/>
+      <c r="N142" s="211" t="n"/>
+      <c r="O142" s="211" t="n"/>
+      <c r="P142" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L142" s="210" t="n"/>
-      <c r="M142" s="211" t="n"/>
-      <c r="N142" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O142" s="211" t="n"/>
-      <c r="P142" s="211" t="n"/>
       <c r="Q142" s="233" t="n"/>
       <c r="R142" s="212" t="n"/>
       <c r="S142" s="233" t="n"/>
@@ -14983,12 +14983,12 @@
       </c>
       <c r="I143" s="211" t="n"/>
       <c r="J143" s="211" t="n"/>
-      <c r="K143" s="211" t="n"/>
-      <c r="L143" s="210" t="inlineStr">
+      <c r="K143" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L143" s="210" t="n"/>
       <c r="M143" s="211" t="n"/>
       <c r="N143" s="211" t="n"/>
       <c r="O143" s="211" t="n"/>
@@ -15094,13 +15094,13 @@
       </c>
       <c r="K144" s="211" t="n"/>
       <c r="L144" s="210" t="n"/>
-      <c r="M144" s="211" t="n"/>
+      <c r="M144" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N144" s="211" t="n"/>
-      <c r="O144" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O144" s="211" t="n"/>
       <c r="P144" s="211" t="n"/>
       <c r="Q144" s="233" t="n"/>
       <c r="R144" s="212" t="n"/>
@@ -15191,13 +15191,13 @@
       <c r="J145" s="211" t="n"/>
       <c r="K145" s="211" t="n"/>
       <c r="L145" s="210" t="n"/>
-      <c r="M145" s="211" t="n"/>
+      <c r="M145" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N145" s="211" t="n"/>
-      <c r="O145" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O145" s="211" t="n"/>
       <c r="P145" s="211" t="n"/>
       <c r="Q145" s="233" t="n"/>
       <c r="R145" s="212" t="n"/>
@@ -15263,20 +15263,20 @@
         </is>
       </c>
       <c r="J146" s="211" t="n"/>
-      <c r="K146" s="211" t="inlineStr">
+      <c r="K146" s="211" t="n"/>
+      <c r="L146" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M146" s="211" t="n"/>
+      <c r="N146" s="211" t="n"/>
+      <c r="O146" s="211" t="n"/>
+      <c r="P146" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L146" s="210" t="n"/>
-      <c r="M146" s="211" t="n"/>
-      <c r="N146" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O146" s="211" t="n"/>
-      <c r="P146" s="211" t="n"/>
       <c r="Q146" s="233" t="n"/>
       <c r="R146" s="212" t="n"/>
       <c r="S146" s="233" t="n"/>
@@ -15374,13 +15374,13 @@
       </c>
       <c r="K147" s="211" t="n"/>
       <c r="L147" s="210" t="n"/>
-      <c r="M147" s="211" t="n"/>
+      <c r="M147" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N147" s="211" t="n"/>
-      <c r="O147" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O147" s="211" t="n"/>
       <c r="P147" s="211" t="n"/>
       <c r="Q147" s="233" t="n"/>
       <c r="R147" s="212" t="n"/>
@@ -15542,13 +15542,13 @@
       </c>
       <c r="K149" s="211" t="n"/>
       <c r="L149" s="210" t="n"/>
-      <c r="M149" s="211" t="n"/>
+      <c r="M149" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N149" s="211" t="n"/>
-      <c r="O149" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O149" s="211" t="n"/>
       <c r="P149" s="211" t="n"/>
       <c r="Q149" s="233" t="n"/>
       <c r="R149" s="212" t="n"/>
@@ -15608,13 +15608,13 @@
       </c>
       <c r="J150" s="211" t="n"/>
       <c r="K150" s="211" t="n"/>
-      <c r="L150" s="210" t="n"/>
+      <c r="L150" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M150" s="211" t="n"/>
-      <c r="N150" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N150" s="211" t="n"/>
       <c r="O150" s="211" t="n"/>
       <c r="P150" s="211" t="n"/>
       <c r="Q150" s="233" t="n"/>
@@ -15682,28 +15682,28 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K151" s="211" t="n"/>
+      <c r="K151" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="L151" s="210" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M151" s="211" t="n"/>
+      <c r="M151" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N151" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O151" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P151" s="211" t="inlineStr">
-        <is>
           <t>〇</t>
         </is>
       </c>
+      <c r="O151" s="211" t="n"/>
+      <c r="P151" s="211" t="n"/>
       <c r="Q151" s="233" t="n"/>
       <c r="R151" s="212" t="n"/>
       <c r="S151" s="233" t="n"/>
@@ -15781,19 +15781,19 @@
         </is>
       </c>
       <c r="J152" s="211" t="n"/>
-      <c r="K152" s="211" t="n"/>
-      <c r="L152" s="210" t="inlineStr">
+      <c r="K152" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
-      <c r="M152" s="211" t="n"/>
+      <c r="L152" s="210" t="n"/>
+      <c r="M152" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N152" s="211" t="n"/>
-      <c r="O152" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O152" s="211" t="n"/>
       <c r="P152" s="211" t="n"/>
       <c r="Q152" s="233" t="n"/>
       <c r="R152" s="212" t="n"/>
@@ -15853,13 +15853,13 @@
       <c r="I153" s="211" t="n"/>
       <c r="J153" s="211" t="n"/>
       <c r="K153" s="211" t="n"/>
-      <c r="L153" s="210" t="n"/>
+      <c r="L153" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M153" s="211" t="n"/>
-      <c r="N153" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N153" s="211" t="n"/>
       <c r="O153" s="211" t="n"/>
       <c r="P153" s="211" t="n"/>
       <c r="Q153" s="233" t="n"/>
@@ -15920,13 +15920,13 @@
       </c>
       <c r="J154" s="211" t="n"/>
       <c r="K154" s="211" t="n"/>
-      <c r="L154" s="210" t="n"/>
+      <c r="L154" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M154" s="211" t="n"/>
-      <c r="N154" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N154" s="211" t="n"/>
       <c r="O154" s="211" t="n"/>
       <c r="P154" s="211" t="n"/>
       <c r="Q154" s="233" t="n"/>
@@ -15984,13 +15984,13 @@
       <c r="J155" s="211" t="n"/>
       <c r="K155" s="211" t="n"/>
       <c r="L155" s="210" t="n"/>
-      <c r="M155" s="211" t="n"/>
+      <c r="M155" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N155" s="211" t="n"/>
-      <c r="O155" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O155" s="211" t="n"/>
       <c r="P155" s="211" t="n"/>
       <c r="Q155" s="233" t="n"/>
       <c r="R155" s="212" t="n"/>
@@ -16055,26 +16055,26 @@
       </c>
       <c r="K156" s="233" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L156" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M156" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N156" s="211" t="n"/>
+      <c r="O156" s="211" t="n"/>
+      <c r="P156" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L156" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M156" s="211" t="n"/>
-      <c r="N156" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O156" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P156" s="211" t="n"/>
       <c r="Q156" s="233" t="n"/>
       <c r="R156" s="212" t="n"/>
       <c r="S156" s="233" t="n"/>
@@ -16158,28 +16158,28 @@
       </c>
       <c r="K157" s="233" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L157" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M157" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N157" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="O157" s="211" t="n"/>
+      <c r="P157" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L157" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M157" s="211" t="n"/>
-      <c r="N157" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O157" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P157" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
       <c r="Q157" s="233" t="n"/>
@@ -16256,13 +16256,13 @@
       <c r="I158" s="211" t="n"/>
       <c r="J158" s="211" t="n"/>
       <c r="K158" s="211" t="n"/>
-      <c r="L158" s="210" t="n"/>
+      <c r="L158" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M158" s="211" t="n"/>
-      <c r="N158" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N158" s="211" t="n"/>
       <c r="O158" s="211" t="n"/>
       <c r="P158" s="211" t="n"/>
       <c r="Q158" s="233" t="n"/>
@@ -16328,13 +16328,13 @@
       </c>
       <c r="K159" s="211" t="n"/>
       <c r="L159" s="210" t="n"/>
-      <c r="M159" s="211" t="n"/>
+      <c r="M159" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N159" s="211" t="n"/>
-      <c r="O159" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O159" s="211" t="n"/>
       <c r="P159" s="211" t="n"/>
       <c r="Q159" s="233" t="n"/>
       <c r="R159" s="212" t="inlineStr">
@@ -16397,20 +16397,20 @@
         </is>
       </c>
       <c r="J160" s="211" t="n"/>
-      <c r="K160" s="211" t="inlineStr">
+      <c r="K160" s="211" t="n"/>
+      <c r="L160" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M160" s="211" t="n"/>
+      <c r="N160" s="211" t="n"/>
+      <c r="O160" s="211" t="n"/>
+      <c r="P160" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L160" s="210" t="n"/>
-      <c r="M160" s="211" t="n"/>
-      <c r="N160" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O160" s="211" t="n"/>
-      <c r="P160" s="211" t="n"/>
       <c r="Q160" s="233" t="n"/>
       <c r="R160" s="212" t="n"/>
       <c r="S160" s="233" t="n"/>
@@ -16470,13 +16470,13 @@
       <c r="J161" s="211" t="n"/>
       <c r="K161" s="211" t="n"/>
       <c r="L161" s="210" t="n"/>
-      <c r="M161" s="211" t="n"/>
+      <c r="M161" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N161" s="211" t="n"/>
-      <c r="O161" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O161" s="211" t="n"/>
       <c r="P161" s="211" t="n"/>
       <c r="Q161" s="233" t="n"/>
       <c r="R161" s="212" t="n"/>
@@ -16533,13 +16533,13 @@
       <c r="J162" s="211" t="n"/>
       <c r="K162" s="211" t="n"/>
       <c r="L162" s="210" t="n"/>
-      <c r="M162" s="211" t="n"/>
+      <c r="M162" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N162" s="211" t="n"/>
-      <c r="O162" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O162" s="211" t="n"/>
       <c r="P162" s="211" t="n"/>
       <c r="Q162" s="233" t="n"/>
       <c r="R162" s="212" t="n"/>
@@ -16596,13 +16596,13 @@
       <c r="J163" s="211" t="n"/>
       <c r="K163" s="211" t="n"/>
       <c r="L163" s="210" t="n"/>
-      <c r="M163" s="211" t="n"/>
+      <c r="M163" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N163" s="211" t="n"/>
-      <c r="O163" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O163" s="211" t="n"/>
       <c r="P163" s="211" t="n"/>
       <c r="Q163" s="233" t="n"/>
       <c r="R163" s="212" t="n"/>
@@ -16660,13 +16660,13 @@
       <c r="K164" s="211" t="n"/>
       <c r="L164" s="210" t="n"/>
       <c r="M164" s="211" t="n"/>
-      <c r="N164" s="211" t="n"/>
+      <c r="N164" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="O164" s="211" t="n"/>
-      <c r="P164" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
+      <c r="P164" s="211" t="n"/>
       <c r="Q164" s="233" t="n"/>
       <c r="R164" s="212" t="n"/>
       <c r="S164" s="233" t="n"/>
@@ -16725,13 +16725,13 @@
       </c>
       <c r="J165" s="211" t="n"/>
       <c r="K165" s="211" t="n"/>
-      <c r="L165" s="210" t="n"/>
+      <c r="L165" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M165" s="211" t="n"/>
-      <c r="N165" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N165" s="211" t="n"/>
       <c r="O165" s="211" t="n"/>
       <c r="P165" s="211" t="n"/>
       <c r="Q165" s="233" t="n"/>
@@ -16791,20 +16791,20 @@
         </is>
       </c>
       <c r="J166" s="211" t="n"/>
-      <c r="K166" s="211" t="inlineStr">
+      <c r="K166" s="211" t="n"/>
+      <c r="L166" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M166" s="211" t="n"/>
+      <c r="N166" s="211" t="n"/>
+      <c r="O166" s="211" t="n"/>
+      <c r="P166" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L166" s="210" t="n"/>
-      <c r="M166" s="211" t="n"/>
-      <c r="N166" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O166" s="211" t="n"/>
-      <c r="P166" s="211" t="n"/>
       <c r="Q166" s="233" t="n"/>
       <c r="R166" s="212" t="n"/>
       <c r="S166" s="233" t="n"/>
@@ -16863,13 +16863,13 @@
       <c r="I167" s="211" t="n"/>
       <c r="J167" s="211" t="n"/>
       <c r="K167" s="211" t="n"/>
-      <c r="L167" s="210" t="n"/>
+      <c r="L167" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M167" s="211" t="n"/>
-      <c r="N167" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N167" s="211" t="n"/>
       <c r="O167" s="211" t="n"/>
       <c r="P167" s="211" t="n"/>
       <c r="Q167" s="233" t="n"/>
@@ -16931,13 +16931,13 @@
       </c>
       <c r="K168" s="211" t="n"/>
       <c r="L168" s="210" t="n"/>
-      <c r="M168" s="211" t="n"/>
+      <c r="M168" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N168" s="211" t="n"/>
-      <c r="O168" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O168" s="211" t="n"/>
       <c r="P168" s="211" t="n"/>
       <c r="Q168" s="233" t="n"/>
       <c r="R168" s="212" t="n"/>
@@ -17002,22 +17002,22 @@
       <c r="J169" s="211" t="n"/>
       <c r="K169" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L169" s="210" t="n"/>
+      <c r="M169" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N169" s="211" t="n"/>
+      <c r="O169" s="211" t="n"/>
+      <c r="P169" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L169" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M169" s="211" t="n"/>
-      <c r="N169" s="211" t="n"/>
-      <c r="O169" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P169" s="211" t="n"/>
       <c r="Q169" s="233" t="n"/>
       <c r="R169" s="212" t="n"/>
       <c r="S169" s="233" t="n"/>
@@ -17076,13 +17076,13 @@
       <c r="I170" s="211" t="n"/>
       <c r="J170" s="211" t="n"/>
       <c r="K170" s="211" t="n"/>
-      <c r="L170" s="210" t="n"/>
+      <c r="L170" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M170" s="211" t="n"/>
-      <c r="N170" s="233" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N170" s="233" t="n"/>
       <c r="O170" s="211" t="n"/>
       <c r="P170" s="211" t="n"/>
       <c r="Q170" s="233" t="n"/>
@@ -17142,12 +17142,12 @@
       </c>
       <c r="I171" s="211" t="n"/>
       <c r="J171" s="211" t="n"/>
-      <c r="K171" s="211" t="n"/>
-      <c r="L171" s="210" t="inlineStr">
+      <c r="K171" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L171" s="210" t="n"/>
       <c r="M171" s="211" t="n"/>
       <c r="N171" s="211" t="n"/>
       <c r="O171" s="211" t="n"/>
@@ -17223,28 +17223,28 @@
       </c>
       <c r="K172" s="211" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="L172" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M172" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N172" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="O172" s="211" t="n"/>
+      <c r="P172" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L172" s="210" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="M172" s="211" t="n"/>
-      <c r="N172" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O172" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P172" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
       <c r="Q172" s="233" t="n"/>
@@ -17381,13 +17381,13 @@
       </c>
       <c r="K174" s="211" t="n"/>
       <c r="L174" s="210" t="n"/>
-      <c r="M174" s="211" t="n"/>
+      <c r="M174" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N174" s="211" t="n"/>
-      <c r="O174" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O174" s="211" t="n"/>
       <c r="P174" s="211" t="n"/>
       <c r="Q174" s="233" t="n"/>
       <c r="R174" s="212" t="n"/>
@@ -17456,13 +17456,13 @@
       </c>
       <c r="K175" s="211" t="n"/>
       <c r="L175" s="210" t="n"/>
-      <c r="M175" s="211" t="n"/>
+      <c r="M175" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N175" s="211" t="n"/>
-      <c r="O175" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O175" s="211" t="n"/>
       <c r="P175" s="211" t="n"/>
       <c r="Q175" s="233" t="n"/>
       <c r="R175" s="212" t="n"/>
@@ -17519,13 +17519,13 @@
       <c r="J176" s="211" t="n"/>
       <c r="K176" s="211" t="n"/>
       <c r="L176" s="210" t="n"/>
-      <c r="M176" s="211" t="n"/>
+      <c r="M176" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N176" s="211" t="n"/>
-      <c r="O176" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O176" s="211" t="n"/>
       <c r="P176" s="211" t="n"/>
       <c r="Q176" s="233" t="n"/>
       <c r="R176" s="212" t="n"/>
@@ -17580,20 +17580,20 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K177" s="233" t="inlineStr">
+      <c r="K177" s="233" t="n"/>
+      <c r="L177" s="210" t="n"/>
+      <c r="M177" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N177" s="211" t="n"/>
+      <c r="O177" s="211" t="n"/>
+      <c r="P177" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L177" s="210" t="n"/>
-      <c r="M177" s="211" t="n"/>
-      <c r="N177" s="211" t="n"/>
-      <c r="O177" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P177" s="211" t="n"/>
       <c r="Q177" s="233" t="n"/>
       <c r="R177" s="212" t="n"/>
       <c r="S177" s="233" t="n"/>
@@ -17651,20 +17651,20 @@
           <t>N-</t>
         </is>
       </c>
-      <c r="K178" s="233" t="inlineStr">
+      <c r="K178" s="233" t="n"/>
+      <c r="L178" s="210" t="n"/>
+      <c r="M178" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="N178" s="211" t="n"/>
+      <c r="O178" s="211" t="n"/>
+      <c r="P178" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L178" s="210" t="n"/>
-      <c r="M178" s="211" t="n"/>
-      <c r="N178" s="211" t="n"/>
-      <c r="O178" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="P178" s="211" t="n"/>
       <c r="Q178" s="233" t="n"/>
       <c r="R178" s="212" t="n"/>
       <c r="S178" s="233" t="n"/>
@@ -17720,18 +17720,18 @@
       <c r="J179" s="211" t="n"/>
       <c r="K179" s="211" t="inlineStr">
         <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="L179" s="210" t="inlineStr">
-        <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L179" s="210" t="n"/>
       <c r="M179" s="211" t="n"/>
       <c r="N179" s="211" t="n"/>
       <c r="O179" s="211" t="n"/>
-      <c r="P179" s="211" t="n"/>
+      <c r="P179" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
       <c r="Q179" s="233" t="n"/>
       <c r="R179" s="212" t="n"/>
       <c r="S179" s="233" t="n"/>
@@ -17787,13 +17787,13 @@
       </c>
       <c r="K180" s="211" t="n"/>
       <c r="L180" s="210" t="n"/>
-      <c r="M180" s="211" t="n"/>
+      <c r="M180" s="211" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="N180" s="211" t="n"/>
-      <c r="O180" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="O180" s="211" t="n"/>
       <c r="P180" s="211" t="n"/>
       <c r="Q180" s="233" t="n"/>
       <c r="R180" s="212" t="n"/>
@@ -17856,20 +17856,20 @@
       </c>
       <c r="I181" s="211" t="n"/>
       <c r="J181" s="211" t="n"/>
-      <c r="K181" s="211" t="n"/>
-      <c r="L181" s="210" t="inlineStr">
+      <c r="K181" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L181" s="210" t="n"/>
       <c r="M181" s="211" t="n"/>
-      <c r="N181" s="211" t="n"/>
+      <c r="N181" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="O181" s="211" t="n"/>
-      <c r="P181" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
+      <c r="P181" s="211" t="n"/>
       <c r="Q181" s="233" t="n"/>
       <c r="R181" s="212" t="n"/>
       <c r="S181" s="233" t="n"/>
@@ -17927,20 +17927,20 @@
       </c>
       <c r="I182" s="211" t="n"/>
       <c r="J182" s="211" t="n"/>
-      <c r="K182" s="211" t="n"/>
-      <c r="L182" s="210" t="inlineStr">
+      <c r="K182" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L182" s="210" t="n"/>
       <c r="M182" s="211" t="n"/>
-      <c r="N182" s="211" t="n"/>
+      <c r="N182" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="O182" s="211" t="n"/>
-      <c r="P182" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
+      <c r="P182" s="211" t="n"/>
       <c r="Q182" s="233" t="n"/>
       <c r="R182" s="212" t="n"/>
       <c r="S182" s="233" t="n"/>
@@ -18002,20 +18002,20 @@
       </c>
       <c r="I183" s="211" t="n"/>
       <c r="J183" s="211" t="n"/>
-      <c r="K183" s="211" t="n"/>
-      <c r="L183" s="210" t="inlineStr">
+      <c r="K183" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L183" s="210" t="n"/>
       <c r="M183" s="211" t="n"/>
-      <c r="N183" s="211" t="n"/>
+      <c r="N183" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="O183" s="211" t="n"/>
-      <c r="P183" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
+      <c r="P183" s="211" t="n"/>
       <c r="Q183" s="233" t="n"/>
       <c r="R183" s="212" t="n"/>
       <c r="S183" s="233" t="n"/>
@@ -18134,22 +18134,22 @@
       <c r="J185" s="211" t="n"/>
       <c r="K185" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L185" s="210" t="n"/>
+      <c r="M185" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N185" s="211" t="n"/>
+      <c r="O185" s="211" t="n"/>
+      <c r="P185" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L185" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M185" s="211" t="n"/>
-      <c r="N185" s="211" t="n"/>
-      <c r="O185" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P185" s="211" t="n"/>
       <c r="Q185" s="233" t="n"/>
       <c r="R185" s="212" t="n"/>
       <c r="S185" s="233" t="n"/>
@@ -18255,22 +18255,22 @@
       <c r="J186" s="211" t="n"/>
       <c r="K186" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L186" s="210" t="n"/>
+      <c r="M186" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N186" s="211" t="n"/>
+      <c r="O186" s="211" t="n"/>
+      <c r="P186" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L186" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M186" s="211" t="n"/>
-      <c r="N186" s="211" t="n"/>
-      <c r="O186" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P186" s="211" t="n"/>
       <c r="Q186" s="233" t="n"/>
       <c r="R186" s="212" t="n"/>
       <c r="S186" s="233" t="n"/>
@@ -18366,12 +18366,12 @@
       </c>
       <c r="I187" s="211" t="n"/>
       <c r="J187" s="211" t="n"/>
-      <c r="K187" s="211" t="n"/>
-      <c r="L187" s="210" t="inlineStr">
+      <c r="K187" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L187" s="210" t="n"/>
       <c r="M187" s="211" t="n"/>
       <c r="N187" s="211" t="n"/>
       <c r="O187" s="211" t="n"/>
@@ -18463,12 +18463,12 @@
       </c>
       <c r="I188" s="211" t="n"/>
       <c r="J188" s="211" t="n"/>
-      <c r="K188" s="211" t="n"/>
-      <c r="L188" s="210" t="inlineStr">
+      <c r="K188" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L188" s="210" t="n"/>
       <c r="M188" s="211" t="n"/>
       <c r="N188" s="211" t="n"/>
       <c r="O188" s="211" t="n"/>
@@ -18566,13 +18566,13 @@
       </c>
       <c r="K189" s="211" t="n"/>
       <c r="L189" s="210" t="n"/>
-      <c r="M189" s="211" t="n"/>
+      <c r="M189" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N189" s="211" t="n"/>
-      <c r="O189" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O189" s="211" t="n"/>
       <c r="P189" s="211" t="n"/>
       <c r="Q189" s="233" t="n"/>
       <c r="R189" s="212" t="n"/>
@@ -18671,13 +18671,13 @@
       </c>
       <c r="K190" s="211" t="n"/>
       <c r="L190" s="210" t="n"/>
-      <c r="M190" s="211" t="n"/>
+      <c r="M190" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N190" s="211" t="n"/>
-      <c r="O190" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O190" s="211" t="n"/>
       <c r="P190" s="211" t="n"/>
       <c r="Q190" s="233" t="n"/>
       <c r="R190" s="212" t="n"/>
@@ -18772,13 +18772,13 @@
       <c r="J191" s="211" t="n"/>
       <c r="K191" s="211" t="n"/>
       <c r="L191" s="210" t="n"/>
-      <c r="M191" s="211" t="n"/>
+      <c r="M191" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N191" s="211" t="n"/>
-      <c r="O191" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O191" s="211" t="n"/>
       <c r="P191" s="211" t="n"/>
       <c r="Q191" s="233" t="n"/>
       <c r="R191" s="212" t="n"/>
@@ -18852,28 +18852,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K192" s="211" t="n"/>
+      <c r="K192" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L192" s="210" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M192" s="211" t="n"/>
+      <c r="M192" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N192" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O192" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P192" s="211" t="inlineStr">
-        <is>
           <t>△</t>
         </is>
       </c>
+      <c r="O192" s="211" t="n"/>
+      <c r="P192" s="211" t="n"/>
       <c r="Q192" s="233" t="n"/>
       <c r="R192" s="212" t="n"/>
       <c r="S192" s="233" t="n"/>
@@ -18989,28 +18989,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K193" s="211" t="n"/>
+      <c r="K193" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L193" s="210" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M193" s="211" t="n"/>
+      <c r="M193" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N193" s="211" t="inlineStr">
         <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O193" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P193" s="211" t="inlineStr">
-        <is>
           <t>△</t>
         </is>
       </c>
+      <c r="O193" s="211" t="n"/>
+      <c r="P193" s="211" t="n"/>
       <c r="Q193" s="233" t="n"/>
       <c r="R193" s="212" t="n"/>
       <c r="S193" s="233" t="n"/>
@@ -19079,7 +19079,7 @@
       <c r="G194" s="233" t="n"/>
       <c r="H194" s="211" t="inlineStr">
         <is>
-          <t>　　　</t>
+          <t xml:space="preserve">　　　</t>
         </is>
       </c>
       <c r="I194" s="211" t="inlineStr">
@@ -19088,20 +19088,20 @@
         </is>
       </c>
       <c r="J194" s="211" t="n"/>
-      <c r="K194" s="211" t="inlineStr">
+      <c r="K194" s="211" t="n"/>
+      <c r="L194" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M194" s="211" t="n"/>
+      <c r="N194" s="211" t="n"/>
+      <c r="O194" s="211" t="n"/>
+      <c r="P194" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L194" s="210" t="n"/>
-      <c r="M194" s="211" t="n"/>
-      <c r="N194" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O194" s="211" t="n"/>
-      <c r="P194" s="211" t="n"/>
       <c r="Q194" s="233" t="n"/>
       <c r="R194" s="212" t="n"/>
       <c r="S194" s="233" t="n"/>
@@ -19199,22 +19199,22 @@
       <c r="J195" s="211" t="n"/>
       <c r="K195" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L195" s="210" t="n"/>
+      <c r="M195" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N195" s="211" t="n"/>
+      <c r="O195" s="211" t="n"/>
+      <c r="P195" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L195" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M195" s="211" t="n"/>
-      <c r="N195" s="211" t="n"/>
-      <c r="O195" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P195" s="211" t="n"/>
       <c r="Q195" s="233" t="n"/>
       <c r="R195" s="212" t="n"/>
       <c r="S195" s="233" t="n"/>
@@ -19278,13 +19278,13 @@
       <c r="J196" s="211" t="n"/>
       <c r="K196" s="211" t="n"/>
       <c r="L196" s="210" t="n"/>
-      <c r="M196" s="211" t="n"/>
+      <c r="M196" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N196" s="211" t="n"/>
-      <c r="O196" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O196" s="211" t="n"/>
       <c r="P196" s="211" t="n"/>
       <c r="Q196" s="233" t="n"/>
       <c r="R196" s="212" t="n"/>
@@ -19341,13 +19341,13 @@
       <c r="J197" s="211" t="n"/>
       <c r="K197" s="211" t="n"/>
       <c r="L197" s="210" t="n"/>
-      <c r="M197" s="211" t="n"/>
+      <c r="M197" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N197" s="211" t="n"/>
-      <c r="O197" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O197" s="211" t="n"/>
       <c r="P197" s="211" t="n"/>
       <c r="Q197" s="233" t="n"/>
       <c r="R197" s="212" t="n"/>
@@ -19408,13 +19408,13 @@
       </c>
       <c r="K198" s="211" t="n"/>
       <c r="L198" s="210" t="n"/>
-      <c r="M198" s="211" t="n"/>
+      <c r="M198" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N198" s="211" t="n"/>
-      <c r="O198" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O198" s="211" t="n"/>
       <c r="P198" s="211" t="n"/>
       <c r="Q198" s="233" t="n"/>
       <c r="R198" s="212" t="n"/>
@@ -19475,13 +19475,13 @@
       </c>
       <c r="K199" s="211" t="n"/>
       <c r="L199" s="210" t="n"/>
-      <c r="M199" s="211" t="n"/>
+      <c r="M199" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N199" s="211" t="n"/>
-      <c r="O199" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O199" s="211" t="n"/>
       <c r="P199" s="211" t="n"/>
       <c r="Q199" s="233" t="n"/>
       <c r="R199" s="212" t="n"/>
@@ -19549,13 +19549,13 @@
       </c>
       <c r="J200" s="211" t="n"/>
       <c r="K200" s="211" t="n"/>
-      <c r="L200" s="210" t="n"/>
+      <c r="L200" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M200" s="211" t="n"/>
-      <c r="N200" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N200" s="211" t="n"/>
       <c r="O200" s="211" t="n"/>
       <c r="P200" s="211" t="n"/>
       <c r="Q200" s="233" t="n"/>
@@ -19623,19 +19623,19 @@
         </is>
       </c>
       <c r="J201" s="211" t="n"/>
-      <c r="K201" s="211" t="n"/>
-      <c r="L201" s="210" t="inlineStr">
+      <c r="K201" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M201" s="211" t="n"/>
+      <c r="L201" s="210" t="n"/>
+      <c r="M201" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N201" s="211" t="n"/>
-      <c r="O201" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O201" s="211" t="n"/>
       <c r="P201" s="211" t="n"/>
       <c r="Q201" s="233" t="n"/>
       <c r="R201" s="212" t="n"/>
@@ -19708,13 +19708,13 @@
       </c>
       <c r="K202" s="211" t="n"/>
       <c r="L202" s="210" t="n"/>
-      <c r="M202" s="211" t="n"/>
+      <c r="M202" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N202" s="211" t="n"/>
-      <c r="O202" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O202" s="211" t="n"/>
       <c r="P202" s="211" t="n"/>
       <c r="Q202" s="233" t="n"/>
       <c r="R202" s="212" t="n"/>
@@ -19771,13 +19771,13 @@
       <c r="J203" s="211" t="n"/>
       <c r="K203" s="211" t="n"/>
       <c r="L203" s="210" t="n"/>
-      <c r="M203" s="211" t="n"/>
+      <c r="M203" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N203" s="211" t="n"/>
-      <c r="O203" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O203" s="211" t="n"/>
       <c r="P203" s="211" t="n"/>
       <c r="Q203" s="233" t="n"/>
       <c r="R203" s="212" t="n"/>
@@ -19838,13 +19838,13 @@
       </c>
       <c r="K204" s="211" t="n"/>
       <c r="L204" s="210" t="n"/>
-      <c r="M204" s="211" t="n"/>
+      <c r="M204" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N204" s="211" t="n"/>
-      <c r="O204" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O204" s="211" t="n"/>
       <c r="P204" s="211" t="n"/>
       <c r="Q204" s="233" t="n"/>
       <c r="R204" s="212" t="n"/>
@@ -19905,13 +19905,13 @@
       <c r="J205" s="211" t="n"/>
       <c r="K205" s="211" t="n"/>
       <c r="L205" s="210" t="n"/>
-      <c r="M205" s="211" t="n"/>
+      <c r="M205" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N205" s="211" t="n"/>
-      <c r="O205" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O205" s="211" t="n"/>
       <c r="P205" s="211" t="n"/>
       <c r="Q205" s="233" t="n"/>
       <c r="R205" s="212" t="n"/>
@@ -19964,13 +19964,13 @@
       <c r="J206" s="211" t="n"/>
       <c r="K206" s="211" t="n"/>
       <c r="L206" s="210" t="n"/>
-      <c r="M206" s="211" t="n"/>
+      <c r="M206" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N206" s="211" t="n"/>
-      <c r="O206" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O206" s="211" t="n"/>
       <c r="P206" s="211" t="n"/>
       <c r="Q206" s="233" t="n"/>
       <c r="R206" s="212" t="n"/>
@@ -20027,13 +20027,13 @@
       <c r="J207" s="211" t="n"/>
       <c r="K207" s="211" t="n"/>
       <c r="L207" s="210" t="n"/>
-      <c r="M207" s="211" t="n"/>
+      <c r="M207" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N207" s="211" t="n"/>
-      <c r="O207" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O207" s="211" t="n"/>
       <c r="P207" s="211" t="n"/>
       <c r="Q207" s="233" t="n"/>
       <c r="R207" s="212" t="n"/>
@@ -20094,13 +20094,13 @@
       <c r="J208" s="211" t="n"/>
       <c r="K208" s="211" t="n"/>
       <c r="L208" s="210" t="n"/>
-      <c r="M208" s="211" t="n"/>
+      <c r="M208" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N208" s="211" t="n"/>
-      <c r="O208" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O208" s="211" t="n"/>
       <c r="P208" s="211" t="n"/>
       <c r="Q208" s="233" t="n"/>
       <c r="R208" s="212" t="n"/>
@@ -20160,13 +20160,13 @@
       </c>
       <c r="J209" s="211" t="n"/>
       <c r="K209" s="211" t="n"/>
-      <c r="L209" s="210" t="n"/>
+      <c r="L209" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M209" s="211" t="n"/>
-      <c r="N209" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N209" s="211" t="n"/>
       <c r="O209" s="211" t="n"/>
       <c r="P209" s="211" t="n"/>
       <c r="Q209" s="233" t="n"/>
@@ -20224,13 +20224,13 @@
       <c r="J210" s="211" t="n"/>
       <c r="K210" s="211" t="n"/>
       <c r="L210" s="210" t="n"/>
-      <c r="M210" s="211" t="n"/>
+      <c r="M210" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N210" s="211" t="n"/>
-      <c r="O210" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O210" s="211" t="n"/>
       <c r="P210" s="211" t="n"/>
       <c r="Q210" s="233" t="n"/>
       <c r="R210" s="212" t="n"/>
@@ -20289,18 +20289,18 @@
       </c>
       <c r="I211" s="211" t="n"/>
       <c r="J211" s="211" t="n"/>
-      <c r="K211" s="211" t="n"/>
+      <c r="K211" s="211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　</t>
+        </is>
+      </c>
       <c r="L211" s="210" t="inlineStr">
         <is>
-          <t>　</t>
+          <t>K-</t>
         </is>
       </c>
       <c r="M211" s="211" t="n"/>
-      <c r="N211" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N211" s="211" t="n"/>
       <c r="O211" s="211" t="n"/>
       <c r="P211" s="211" t="n"/>
       <c r="Q211" s="233" t="n"/>
@@ -20362,13 +20362,13 @@
       </c>
       <c r="K212" s="211" t="n"/>
       <c r="L212" s="210" t="n"/>
-      <c r="M212" s="211" t="n"/>
+      <c r="M212" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N212" s="211" t="n"/>
-      <c r="O212" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O212" s="211" t="n"/>
       <c r="P212" s="211" t="n"/>
       <c r="Q212" s="233" t="n"/>
       <c r="R212" s="212" t="n"/>
@@ -20431,19 +20431,19 @@
         </is>
       </c>
       <c r="J213" s="211" t="n"/>
-      <c r="K213" s="211" t="n"/>
-      <c r="L213" s="210" t="inlineStr">
+      <c r="K213" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M213" s="211" t="n"/>
+      <c r="L213" s="210" t="n"/>
+      <c r="M213" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N213" s="211" t="n"/>
-      <c r="O213" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O213" s="211" t="n"/>
       <c r="P213" s="211" t="n"/>
       <c r="Q213" s="233" t="n"/>
       <c r="R213" s="212" t="n"/>
@@ -20507,13 +20507,13 @@
       <c r="I214" s="211" t="n"/>
       <c r="J214" s="211" t="n"/>
       <c r="K214" s="211" t="n"/>
-      <c r="L214" s="210" t="n"/>
+      <c r="L214" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M214" s="211" t="n"/>
-      <c r="N214" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N214" s="211" t="n"/>
       <c r="O214" s="211" t="n"/>
       <c r="P214" s="211" t="n"/>
       <c r="Q214" s="233" t="n"/>
@@ -20570,13 +20570,13 @@
       <c r="I215" s="211" t="n"/>
       <c r="J215" s="211" t="n"/>
       <c r="K215" s="211" t="n"/>
-      <c r="L215" s="210" t="n"/>
+      <c r="L215" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M215" s="211" t="n"/>
-      <c r="N215" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N215" s="211" t="n"/>
       <c r="O215" s="211" t="n"/>
       <c r="P215" s="211" t="n"/>
       <c r="Q215" s="233" t="n"/>
@@ -20632,19 +20632,19 @@
         </is>
       </c>
       <c r="J216" s="211" t="n"/>
-      <c r="K216" s="211" t="n"/>
-      <c r="L216" s="210" t="inlineStr">
+      <c r="K216" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M216" s="211" t="n"/>
+      <c r="L216" s="210" t="n"/>
+      <c r="M216" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N216" s="211" t="n"/>
-      <c r="O216" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O216" s="211" t="n"/>
       <c r="P216" s="211" t="n"/>
       <c r="Q216" s="233" t="n"/>
       <c r="R216" s="212" t="n"/>
@@ -20709,13 +20709,13 @@
       </c>
       <c r="K217" s="211" t="n"/>
       <c r="L217" s="210" t="n"/>
-      <c r="M217" s="211" t="n"/>
+      <c r="M217" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N217" s="211" t="n"/>
-      <c r="O217" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O217" s="211" t="n"/>
       <c r="P217" s="211" t="n"/>
       <c r="Q217" s="233" t="n"/>
       <c r="R217" s="212" t="n"/>
@@ -20775,13 +20775,13 @@
       <c r="I218" s="211" t="n"/>
       <c r="J218" s="211" t="n"/>
       <c r="K218" s="211" t="n"/>
-      <c r="L218" s="210" t="n"/>
+      <c r="L218" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M218" s="211" t="n"/>
-      <c r="N218" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N218" s="211" t="n"/>
       <c r="O218" s="211" t="n"/>
       <c r="P218" s="211" t="n"/>
       <c r="Q218" s="233" t="n"/>
@@ -20843,13 +20843,13 @@
       </c>
       <c r="K219" s="211" t="n"/>
       <c r="L219" s="210" t="n"/>
-      <c r="M219" s="211" t="n"/>
+      <c r="M219" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N219" s="211" t="n"/>
-      <c r="O219" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O219" s="211" t="n"/>
       <c r="P219" s="211" t="n"/>
       <c r="Q219" s="233" t="n"/>
       <c r="R219" s="212" t="n"/>
@@ -20912,20 +20912,20 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K220" s="211" t="inlineStr">
+      <c r="K220" s="211" t="n"/>
+      <c r="L220" s="210" t="n"/>
+      <c r="M220" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N220" s="211" t="n"/>
+      <c r="O220" s="211" t="n"/>
+      <c r="P220" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L220" s="210" t="n"/>
-      <c r="M220" s="211" t="n"/>
-      <c r="N220" s="211" t="n"/>
-      <c r="O220" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P220" s="211" t="n"/>
       <c r="Q220" s="233" t="n"/>
       <c r="R220" s="212" t="n"/>
       <c r="S220" s="233" t="n"/>
@@ -20989,13 +20989,13 @@
       </c>
       <c r="K221" s="211" t="n"/>
       <c r="L221" s="210" t="n"/>
-      <c r="M221" s="211" t="n"/>
+      <c r="M221" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N221" s="211" t="n"/>
-      <c r="O221" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O221" s="211" t="n"/>
       <c r="P221" s="211" t="n"/>
       <c r="Q221" s="233" t="n"/>
       <c r="R221" s="212" t="n"/>
@@ -21060,13 +21060,13 @@
       </c>
       <c r="K222" s="211" t="n"/>
       <c r="L222" s="210" t="n"/>
-      <c r="M222" s="211" t="n"/>
+      <c r="M222" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N222" s="211" t="n"/>
-      <c r="O222" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O222" s="211" t="n"/>
       <c r="P222" s="211" t="n"/>
       <c r="Q222" s="233" t="n"/>
       <c r="R222" s="212" t="n"/>
@@ -21129,20 +21129,20 @@
         </is>
       </c>
       <c r="J223" s="211" t="n"/>
-      <c r="K223" s="211" t="inlineStr">
+      <c r="K223" s="211" t="n"/>
+      <c r="L223" s="210" t="n"/>
+      <c r="M223" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N223" s="211" t="n"/>
+      <c r="O223" s="211" t="n"/>
+      <c r="P223" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L223" s="210" t="n"/>
-      <c r="M223" s="211" t="n"/>
-      <c r="N223" s="211" t="n"/>
-      <c r="O223" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P223" s="211" t="n"/>
       <c r="Q223" s="233" t="n"/>
       <c r="R223" s="212" t="inlineStr">
         <is>
@@ -21216,26 +21216,26 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K224" s="211" t="inlineStr">
+      <c r="K224" s="211" t="n"/>
+      <c r="L224" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M224" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N224" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="O224" s="211" t="n"/>
+      <c r="P224" s="211" t="inlineStr">
         <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L224" s="210" t="n"/>
-      <c r="M224" s="211" t="n"/>
-      <c r="N224" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O224" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P224" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
       <c r="Q224" s="233" t="n"/>
@@ -21303,20 +21303,20 @@
       <c r="H225" s="211" t="n"/>
       <c r="I225" s="211" t="n"/>
       <c r="J225" s="211" t="n"/>
-      <c r="K225" s="211" t="inlineStr">
+      <c r="K225" s="211" t="n"/>
+      <c r="L225" s="210" t="n"/>
+      <c r="M225" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
+      <c r="N225" s="211" t="n"/>
+      <c r="O225" s="211" t="n"/>
+      <c r="P225" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L225" s="210" t="n"/>
-      <c r="M225" s="211" t="n"/>
-      <c r="N225" s="211" t="n"/>
-      <c r="O225" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
-      <c r="P225" s="211" t="n"/>
       <c r="Q225" s="233" t="n"/>
       <c r="R225" s="212" t="inlineStr">
         <is>
@@ -21380,13 +21380,13 @@
       </c>
       <c r="K226" s="211" t="n"/>
       <c r="L226" s="210" t="n"/>
-      <c r="M226" s="211" t="n"/>
+      <c r="M226" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N226" s="211" t="n"/>
-      <c r="O226" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O226" s="211" t="n"/>
       <c r="P226" s="211" t="n"/>
       <c r="Q226" s="233" t="n"/>
       <c r="R226" s="212" t="n"/>
@@ -21451,13 +21451,13 @@
       </c>
       <c r="K227" s="211" t="n"/>
       <c r="L227" s="210" t="n"/>
-      <c r="M227" s="211" t="n"/>
+      <c r="M227" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N227" s="211" t="n"/>
-      <c r="O227" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O227" s="211" t="n"/>
       <c r="P227" s="211" t="n"/>
       <c r="Q227" s="233" t="n"/>
       <c r="R227" s="212" t="inlineStr">
@@ -21520,20 +21520,20 @@
       </c>
       <c r="I228" s="211" t="n"/>
       <c r="J228" s="211" t="n"/>
-      <c r="K228" s="211" t="inlineStr">
+      <c r="K228" s="211" t="n"/>
+      <c r="L228" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M228" s="211" t="n"/>
+      <c r="N228" s="211" t="n"/>
+      <c r="O228" s="211" t="n"/>
+      <c r="P228" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L228" s="210" t="n"/>
-      <c r="M228" s="211" t="n"/>
-      <c r="N228" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O228" s="211" t="n"/>
-      <c r="P228" s="211" t="n"/>
       <c r="Q228" s="233" t="n"/>
       <c r="R228" s="212" t="n"/>
       <c r="S228" s="233" t="n"/>
@@ -21630,25 +21630,25 @@
         </is>
       </c>
       <c r="J229" s="211" t="n"/>
-      <c r="K229" s="211" t="n"/>
-      <c r="L229" s="210" t="inlineStr">
+      <c r="K229" s="211" t="inlineStr">
         <is>
           <t>N-</t>
         </is>
       </c>
+      <c r="L229" s="210" t="n"/>
       <c r="M229" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N229" s="211" t="n"/>
+      <c r="O229" s="211" t="n"/>
+      <c r="P229" s="211" t="n"/>
+      <c r="Q229" s="233" t="inlineStr">
+        <is>
           <t>段紙</t>
         </is>
       </c>
-      <c r="N229" s="211" t="n"/>
-      <c r="O229" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P229" s="211" t="n"/>
-      <c r="Q229" s="233" t="n"/>
       <c r="R229" s="212" t="n"/>
       <c r="S229" s="233" t="n"/>
       <c r="T229" s="211" t="n"/>
@@ -21752,20 +21752,20 @@
         </is>
       </c>
       <c r="J230" s="211" t="n"/>
-      <c r="K230" s="211" t="inlineStr">
+      <c r="K230" s="211" t="n"/>
+      <c r="L230" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M230" s="211" t="n"/>
+      <c r="N230" s="211" t="n"/>
+      <c r="O230" s="211" t="n"/>
+      <c r="P230" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L230" s="210" t="n"/>
-      <c r="M230" s="211" t="n"/>
-      <c r="N230" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O230" s="211" t="n"/>
-      <c r="P230" s="211" t="n"/>
       <c r="Q230" s="233" t="n"/>
       <c r="R230" s="212" t="n"/>
       <c r="S230" s="233" t="n"/>
@@ -21861,20 +21861,20 @@
         </is>
       </c>
       <c r="J231" s="211" t="n"/>
-      <c r="K231" s="211" t="inlineStr">
+      <c r="K231" s="211" t="n"/>
+      <c r="L231" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M231" s="211" t="n"/>
+      <c r="N231" s="211" t="n"/>
+      <c r="O231" s="211" t="n"/>
+      <c r="P231" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L231" s="210" t="n"/>
-      <c r="M231" s="211" t="n"/>
-      <c r="N231" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O231" s="211" t="n"/>
-      <c r="P231" s="211" t="n"/>
       <c r="Q231" s="233" t="n"/>
       <c r="R231" s="212" t="n"/>
       <c r="S231" s="233" t="n"/>
@@ -21966,20 +21966,20 @@
         </is>
       </c>
       <c r="J232" s="211" t="n"/>
-      <c r="K232" s="211" t="inlineStr">
+      <c r="K232" s="211" t="n"/>
+      <c r="L232" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M232" s="211" t="n"/>
+      <c r="N232" s="211" t="n"/>
+      <c r="O232" s="211" t="n"/>
+      <c r="P232" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L232" s="210" t="n"/>
-      <c r="M232" s="211" t="n"/>
-      <c r="N232" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O232" s="211" t="n"/>
-      <c r="P232" s="211" t="n"/>
       <c r="Q232" s="233" t="n"/>
       <c r="R232" s="212" t="n"/>
       <c r="S232" s="233" t="n"/>
@@ -22072,13 +22072,13 @@
       </c>
       <c r="J233" s="211" t="n"/>
       <c r="K233" s="211" t="n"/>
-      <c r="L233" s="210" t="n"/>
+      <c r="L233" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="M233" s="211" t="n"/>
-      <c r="N233" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="N233" s="211" t="n"/>
       <c r="O233" s="211" t="n"/>
       <c r="P233" s="211" t="n"/>
       <c r="Q233" s="233" t="n"/>
@@ -22172,20 +22172,20 @@
       </c>
       <c r="I234" s="211" t="n"/>
       <c r="J234" s="211" t="n"/>
-      <c r="K234" s="211" t="inlineStr">
+      <c r="K234" s="211" t="n"/>
+      <c r="L234" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M234" s="211" t="n"/>
+      <c r="N234" s="211" t="n"/>
+      <c r="O234" s="211" t="n"/>
+      <c r="P234" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L234" s="210" t="n"/>
-      <c r="M234" s="211" t="n"/>
-      <c r="N234" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O234" s="211" t="n"/>
-      <c r="P234" s="211" t="n"/>
       <c r="Q234" s="233" t="n"/>
       <c r="R234" s="212" t="n"/>
       <c r="S234" s="233" t="n"/>
@@ -22277,20 +22277,20 @@
       </c>
       <c r="I235" s="211" t="n"/>
       <c r="J235" s="211" t="n"/>
-      <c r="K235" s="211" t="inlineStr">
+      <c r="K235" s="211" t="n"/>
+      <c r="L235" s="210" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="M235" s="211" t="n"/>
+      <c r="N235" s="211" t="n"/>
+      <c r="O235" s="211" t="n"/>
+      <c r="P235" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L235" s="210" t="n"/>
-      <c r="M235" s="211" t="n"/>
-      <c r="N235" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="O235" s="211" t="n"/>
-      <c r="P235" s="211" t="n"/>
       <c r="Q235" s="233" t="n"/>
       <c r="R235" s="212" t="n"/>
       <c r="S235" s="233" t="n"/>
@@ -22483,19 +22483,19 @@
         </is>
       </c>
       <c r="J237" s="211" t="n"/>
-      <c r="K237" s="211" t="n"/>
-      <c r="L237" s="210" t="inlineStr">
+      <c r="K237" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M237" s="211" t="n"/>
+      <c r="L237" s="210" t="n"/>
+      <c r="M237" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N237" s="211" t="n"/>
-      <c r="O237" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O237" s="211" t="n"/>
       <c r="P237" s="211" t="n"/>
       <c r="Q237" s="233" t="n"/>
       <c r="R237" s="212" t="n"/>
@@ -22785,28 +22785,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K241" s="211" t="n"/>
+      <c r="K241" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L241" s="210" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M241" s="211" t="inlineStr">
+        <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M241" s="211" t="n"/>
       <c r="N241" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O241" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P241" s="211" t="inlineStr">
-        <is>
           <t>△</t>
         </is>
       </c>
+      <c r="O241" s="211" t="n"/>
+      <c r="P241" s="211" t="n"/>
       <c r="Q241" s="233" t="n"/>
       <c r="R241" s="212" t="inlineStr">
         <is>
@@ -22886,13 +22886,13 @@
       </c>
       <c r="K242" s="211" t="n"/>
       <c r="L242" s="210" t="n"/>
-      <c r="M242" s="211" t="n"/>
+      <c r="M242" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N242" s="211" t="n"/>
-      <c r="O242" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O242" s="211" t="n"/>
       <c r="P242" s="211" t="n"/>
       <c r="Q242" s="233" t="n"/>
       <c r="R242" s="212" t="n"/>
@@ -22963,28 +22963,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K243" s="211" t="n"/>
+      <c r="K243" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L243" s="210" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M243" s="211" t="inlineStr">
+        <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M243" s="211" t="n"/>
       <c r="N243" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O243" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P243" s="211" t="inlineStr">
-        <is>
           <t>△</t>
         </is>
       </c>
+      <c r="O243" s="211" t="n"/>
+      <c r="P243" s="211" t="n"/>
       <c r="Q243" s="233" t="n"/>
       <c r="R243" s="212" t="inlineStr">
         <is>
@@ -23070,28 +23070,28 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K244" s="211" t="n"/>
+      <c r="K244" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L244" s="210" t="inlineStr">
         <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M244" s="211" t="inlineStr">
+        <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M244" s="211" t="n"/>
       <c r="N244" s="211" t="inlineStr">
         <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O244" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P244" s="211" t="inlineStr">
-        <is>
           <t>△</t>
         </is>
       </c>
+      <c r="O244" s="211" t="n"/>
+      <c r="P244" s="211" t="n"/>
       <c r="Q244" s="233" t="n"/>
       <c r="R244" s="212" t="inlineStr">
         <is>
@@ -23165,12 +23165,12 @@
       <c r="H245" s="211" t="n"/>
       <c r="I245" s="211" t="n"/>
       <c r="J245" s="211" t="n"/>
-      <c r="K245" s="211" t="n"/>
-      <c r="L245" s="210" t="inlineStr">
+      <c r="K245" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L245" s="210" t="n"/>
       <c r="M245" s="211" t="n"/>
       <c r="N245" s="211" t="n"/>
       <c r="O245" s="211" t="n"/>
@@ -23230,18 +23230,18 @@
       <c r="J246" s="211" t="n"/>
       <c r="K246" s="211" t="inlineStr">
         <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="L246" s="210" t="inlineStr">
-        <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L246" s="210" t="n"/>
       <c r="M246" s="211" t="n"/>
       <c r="N246" s="211" t="n"/>
       <c r="O246" s="211" t="n"/>
-      <c r="P246" s="211" t="n"/>
+      <c r="P246" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
       <c r="Q246" s="233" t="n"/>
       <c r="R246" s="212" t="n"/>
       <c r="S246" s="233" t="n"/>
@@ -23297,18 +23297,18 @@
       <c r="J247" s="211" t="n"/>
       <c r="K247" s="211" t="inlineStr">
         <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="L247" s="210" t="inlineStr">
-        <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L247" s="210" t="n"/>
       <c r="M247" s="211" t="n"/>
       <c r="N247" s="211" t="n"/>
       <c r="O247" s="211" t="n"/>
-      <c r="P247" s="211" t="n"/>
+      <c r="P247" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
       <c r="Q247" s="233" t="n"/>
       <c r="R247" s="212" t="n"/>
       <c r="S247" s="233" t="n"/>
@@ -23366,20 +23366,20 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K248" s="211" t="inlineStr">
+      <c r="K248" s="211" t="n"/>
+      <c r="L248" s="210" t="n"/>
+      <c r="M248" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N248" s="211" t="n"/>
+      <c r="O248" s="211" t="n"/>
+      <c r="P248" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L248" s="210" t="n"/>
-      <c r="M248" s="211" t="n"/>
-      <c r="N248" s="211" t="n"/>
-      <c r="O248" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P248" s="211" t="n"/>
       <c r="Q248" s="233" t="n"/>
       <c r="R248" s="212" t="n"/>
       <c r="S248" s="233" t="n"/>
@@ -23434,13 +23434,13 @@
       <c r="I249" s="211" t="n"/>
       <c r="J249" s="211" t="n"/>
       <c r="K249" s="211" t="n"/>
-      <c r="L249" s="210" t="n"/>
+      <c r="L249" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M249" s="211" t="n"/>
-      <c r="N249" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N249" s="211" t="n"/>
       <c r="O249" s="211" t="n"/>
       <c r="P249" s="211" t="n"/>
       <c r="Q249" s="233" t="n"/>
@@ -23494,13 +23494,13 @@
       <c r="J250" s="211" t="n"/>
       <c r="K250" s="211" t="n"/>
       <c r="L250" s="210" t="n"/>
-      <c r="M250" s="211" t="n"/>
+      <c r="M250" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N250" s="211" t="n"/>
-      <c r="O250" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O250" s="211" t="n"/>
       <c r="P250" s="211" t="n"/>
       <c r="Q250" s="233" t="n"/>
       <c r="R250" s="212" t="n"/>
@@ -23557,13 +23557,13 @@
       <c r="J251" s="211" t="n"/>
       <c r="K251" s="211" t="n"/>
       <c r="L251" s="210" t="n"/>
-      <c r="M251" s="211" t="n"/>
+      <c r="M251" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N251" s="211" t="n"/>
-      <c r="O251" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O251" s="211" t="n"/>
       <c r="P251" s="211" t="n"/>
       <c r="Q251" s="233" t="n"/>
       <c r="R251" s="212" t="n"/>
@@ -23614,12 +23614,12 @@
       <c r="H252" s="211" t="n"/>
       <c r="I252" s="211" t="n"/>
       <c r="J252" s="211" t="n"/>
-      <c r="K252" s="211" t="n"/>
-      <c r="L252" s="210" t="inlineStr">
+      <c r="K252" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L252" s="210" t="n"/>
       <c r="M252" s="211" t="n"/>
       <c r="N252" s="211" t="n"/>
       <c r="O252" s="211" t="n"/>
@@ -23683,13 +23683,13 @@
       </c>
       <c r="K253" s="211" t="n"/>
       <c r="L253" s="210" t="n"/>
-      <c r="M253" s="211" t="n"/>
+      <c r="M253" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N253" s="211" t="n"/>
-      <c r="O253" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O253" s="211" t="n"/>
       <c r="P253" s="211" t="n"/>
       <c r="Q253" s="233" t="n"/>
       <c r="R253" s="212" t="n"/>
@@ -23744,12 +23744,12 @@
       <c r="H254" s="211" t="n"/>
       <c r="I254" s="211" t="n"/>
       <c r="J254" s="211" t="n"/>
-      <c r="K254" s="211" t="n"/>
-      <c r="L254" s="210" t="inlineStr">
+      <c r="K254" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L254" s="210" t="n"/>
       <c r="M254" s="211" t="n"/>
       <c r="N254" s="211" t="n"/>
       <c r="O254" s="211" t="n"/>
@@ -23803,12 +23803,12 @@
       <c r="H255" s="211" t="n"/>
       <c r="I255" s="211" t="n"/>
       <c r="J255" s="211" t="n"/>
-      <c r="K255" s="211" t="n"/>
-      <c r="L255" s="210" t="inlineStr">
+      <c r="K255" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L255" s="210" t="n"/>
       <c r="M255" s="211" t="n"/>
       <c r="N255" s="211" t="n"/>
       <c r="O255" s="211" t="n"/>
@@ -23868,18 +23868,18 @@
       <c r="J256" s="211" t="n"/>
       <c r="K256" s="211" t="inlineStr">
         <is>
-          <t>金属</t>
-        </is>
-      </c>
-      <c r="L256" s="210" t="inlineStr">
-        <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L256" s="210" t="n"/>
       <c r="M256" s="211" t="n"/>
       <c r="N256" s="211" t="n"/>
       <c r="O256" s="211" t="n"/>
-      <c r="P256" s="211" t="n"/>
+      <c r="P256" s="211" t="inlineStr">
+        <is>
+          <t>金属</t>
+        </is>
+      </c>
       <c r="Q256" s="233" t="n"/>
       <c r="R256" s="212" t="n"/>
       <c r="S256" s="233" t="n"/>
@@ -23939,13 +23939,13 @@
       <c r="J257" s="211" t="n"/>
       <c r="K257" s="211" t="n"/>
       <c r="L257" s="210" t="n"/>
-      <c r="M257" s="211" t="n"/>
+      <c r="M257" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N257" s="211" t="n"/>
-      <c r="O257" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O257" s="211" t="n"/>
       <c r="P257" s="211" t="n"/>
       <c r="Q257" s="233" t="n"/>
       <c r="R257" s="212" t="n"/>
@@ -24000,18 +24000,18 @@
         </is>
       </c>
       <c r="J258" s="211" t="n"/>
-      <c r="K258" s="211" t="n"/>
+      <c r="K258" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="L258" s="210" t="inlineStr">
         <is>
-          <t>K-</t>
+          <t>N-</t>
         </is>
       </c>
       <c r="M258" s="211" t="n"/>
-      <c r="N258" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N258" s="211" t="n"/>
       <c r="O258" s="211" t="n"/>
       <c r="P258" s="211" t="n"/>
       <c r="Q258" s="233" t="n"/>
@@ -24075,12 +24075,12 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K259" s="211" t="n"/>
-      <c r="L259" s="210" t="inlineStr">
+      <c r="K259" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L259" s="210" t="n"/>
       <c r="M259" s="211" t="n"/>
       <c r="N259" s="211" t="n"/>
       <c r="O259" s="211" t="n"/>
@@ -24148,22 +24148,22 @@
       <c r="J260" s="211" t="n"/>
       <c r="K260" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L260" s="210" t="n"/>
+      <c r="M260" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N260" s="211" t="n"/>
+      <c r="O260" s="211" t="n"/>
+      <c r="P260" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L260" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M260" s="211" t="n"/>
-      <c r="N260" s="211" t="n"/>
-      <c r="O260" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P260" s="211" t="n"/>
       <c r="Q260" s="233" t="n"/>
       <c r="R260" s="212" t="n"/>
       <c r="S260" s="233" t="n"/>
@@ -24221,12 +24221,12 @@
       <c r="H261" s="211" t="n"/>
       <c r="I261" s="211" t="n"/>
       <c r="J261" s="211" t="n"/>
-      <c r="K261" s="211" t="n"/>
-      <c r="L261" s="210" t="inlineStr">
+      <c r="K261" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L261" s="210" t="n"/>
       <c r="M261" s="211" t="n"/>
       <c r="N261" s="211" t="n"/>
       <c r="O261" s="211" t="n"/>
@@ -24294,22 +24294,22 @@
       <c r="J262" s="211" t="n"/>
       <c r="K262" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L262" s="210" t="n"/>
+      <c r="M262" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N262" s="211" t="n"/>
+      <c r="O262" s="211" t="n"/>
+      <c r="P262" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L262" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M262" s="211" t="n"/>
-      <c r="N262" s="211" t="n"/>
-      <c r="O262" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P262" s="211" t="n"/>
       <c r="Q262" s="233" t="n"/>
       <c r="R262" s="212" t="n"/>
       <c r="S262" s="233" t="n"/>
@@ -24377,22 +24377,22 @@
       <c r="J263" s="211" t="n"/>
       <c r="K263" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L263" s="210" t="n"/>
+      <c r="M263" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N263" s="211" t="n"/>
+      <c r="O263" s="211" t="n"/>
+      <c r="P263" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L263" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M263" s="211" t="n"/>
-      <c r="N263" s="211" t="n"/>
-      <c r="O263" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P263" s="211" t="n"/>
       <c r="Q263" s="233" t="n"/>
       <c r="R263" s="212" t="n"/>
       <c r="S263" s="233" t="n"/>
@@ -24456,22 +24456,22 @@
       <c r="J264" s="211" t="n"/>
       <c r="K264" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L264" s="210" t="n"/>
+      <c r="M264" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N264" s="211" t="n"/>
+      <c r="O264" s="211" t="n"/>
+      <c r="P264" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L264" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M264" s="211" t="n"/>
-      <c r="N264" s="211" t="n"/>
-      <c r="O264" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P264" s="211" t="n"/>
       <c r="Q264" s="233" t="n"/>
       <c r="R264" s="212" t="n"/>
       <c r="S264" s="233" t="n"/>
@@ -24535,13 +24535,13 @@
       </c>
       <c r="K265" s="211" t="n"/>
       <c r="L265" s="210" t="n"/>
-      <c r="M265" s="211" t="n"/>
+      <c r="M265" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N265" s="211" t="n"/>
-      <c r="O265" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O265" s="211" t="n"/>
       <c r="P265" s="211" t="n"/>
       <c r="Q265" s="233" t="n"/>
       <c r="R265" s="212" t="n"/>
@@ -24602,13 +24602,13 @@
       <c r="J266" s="211" t="n"/>
       <c r="K266" s="211" t="n"/>
       <c r="L266" s="210" t="n"/>
-      <c r="M266" s="211" t="n"/>
+      <c r="M266" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N266" s="211" t="n"/>
-      <c r="O266" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O266" s="211" t="n"/>
       <c r="P266" s="211" t="n"/>
       <c r="Q266" s="233" t="n"/>
       <c r="R266" s="212" t="inlineStr">
@@ -24669,13 +24669,13 @@
       <c r="J267" s="211" t="n"/>
       <c r="K267" s="211" t="n"/>
       <c r="L267" s="210" t="n"/>
-      <c r="M267" s="211" t="n"/>
+      <c r="M267" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N267" s="211" t="n"/>
-      <c r="O267" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O267" s="211" t="n"/>
       <c r="P267" s="211" t="n"/>
       <c r="Q267" s="233" t="n"/>
       <c r="R267" s="212" t="n"/>
@@ -24731,13 +24731,13 @@
       </c>
       <c r="J268" s="211" t="n"/>
       <c r="K268" s="211" t="n"/>
-      <c r="L268" s="210" t="n"/>
+      <c r="L268" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M268" s="211" t="n"/>
-      <c r="N268" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N268" s="211" t="n"/>
       <c r="O268" s="211" t="n"/>
       <c r="P268" s="211" t="n"/>
       <c r="Q268" s="233" t="n"/>
@@ -24803,28 +24803,28 @@
       </c>
       <c r="K269" s="211" t="inlineStr">
         <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="L269" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
+      <c r="M269" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N269" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="O269" s="211" t="n"/>
+      <c r="P269" s="211" t="inlineStr">
+        <is>
           <t>金属</t>
-        </is>
-      </c>
-      <c r="L269" s="210" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="M269" s="211" t="n"/>
-      <c r="N269" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
-      <c r="O269" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P269" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
         </is>
       </c>
       <c r="Q269" s="233" t="n"/>
@@ -24900,12 +24900,12 @@
       </c>
       <c r="I270" s="211" t="n"/>
       <c r="J270" s="211" t="n"/>
-      <c r="K270" s="211" t="n"/>
-      <c r="L270" s="210" t="inlineStr">
+      <c r="K270" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L270" s="210" t="n"/>
       <c r="M270" s="211" t="n"/>
       <c r="N270" s="211" t="n"/>
       <c r="O270" s="211" t="n"/>
@@ -24977,13 +24977,13 @@
       </c>
       <c r="K271" s="211" t="n"/>
       <c r="L271" s="210" t="n"/>
-      <c r="M271" s="211" t="n"/>
+      <c r="M271" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N271" s="211" t="n"/>
-      <c r="O271" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O271" s="211" t="n"/>
       <c r="P271" s="211" t="n"/>
       <c r="Q271" s="233" t="n"/>
       <c r="R271" s="212" t="n"/>
@@ -25039,13 +25039,13 @@
       <c r="I272" s="211" t="n"/>
       <c r="J272" s="211" t="n"/>
       <c r="K272" s="211" t="n"/>
-      <c r="L272" s="210" t="n"/>
+      <c r="L272" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M272" s="211" t="n"/>
-      <c r="N272" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N272" s="211" t="n"/>
       <c r="O272" s="211" t="n"/>
       <c r="P272" s="211" t="n"/>
       <c r="Q272" s="233" t="n"/>
@@ -25105,20 +25105,20 @@
           <t>K-</t>
         </is>
       </c>
-      <c r="K273" s="211" t="inlineStr">
+      <c r="K273" s="211" t="n"/>
+      <c r="L273" s="210" t="n"/>
+      <c r="M273" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
+      <c r="N273" s="211" t="n"/>
+      <c r="O273" s="211" t="n"/>
+      <c r="P273" s="211" t="inlineStr">
         <is>
           <t>金属</t>
         </is>
       </c>
-      <c r="L273" s="210" t="n"/>
-      <c r="M273" s="211" t="n"/>
-      <c r="N273" s="211" t="n"/>
-      <c r="O273" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
-      <c r="P273" s="211" t="n"/>
       <c r="Q273" s="233" t="n"/>
       <c r="R273" s="212" t="n"/>
       <c r="S273" s="233" t="n"/>
@@ -25180,12 +25180,12 @@
       </c>
       <c r="I274" s="211" t="n"/>
       <c r="J274" s="211" t="n"/>
-      <c r="K274" s="211" t="n"/>
-      <c r="L274" s="210" t="inlineStr">
+      <c r="K274" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L274" s="210" t="n"/>
       <c r="M274" s="211" t="n"/>
       <c r="N274" s="211" t="n"/>
       <c r="O274" s="211" t="n"/>
@@ -25245,13 +25245,13 @@
       </c>
       <c r="K275" s="211" t="n"/>
       <c r="L275" s="210" t="n"/>
-      <c r="M275" s="211" t="n"/>
+      <c r="M275" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N275" s="211" t="n"/>
-      <c r="O275" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O275" s="211" t="n"/>
       <c r="P275" s="211" t="n"/>
       <c r="Q275" s="233" t="n"/>
       <c r="R275" s="212" t="n"/>
@@ -25316,13 +25316,13 @@
       </c>
       <c r="K276" s="211" t="n"/>
       <c r="L276" s="210" t="n"/>
-      <c r="M276" s="211" t="n"/>
+      <c r="M276" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N276" s="211" t="n"/>
-      <c r="O276" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O276" s="211" t="n"/>
       <c r="P276" s="211" t="n"/>
       <c r="Q276" s="233" t="n"/>
       <c r="R276" s="212" t="n"/>
@@ -25387,13 +25387,13 @@
       </c>
       <c r="K277" s="211" t="n"/>
       <c r="L277" s="210" t="n"/>
-      <c r="M277" s="211" t="n"/>
+      <c r="M277" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N277" s="211" t="n"/>
-      <c r="O277" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O277" s="211" t="n"/>
       <c r="P277" s="211" t="n"/>
       <c r="Q277" s="233" t="n"/>
       <c r="R277" s="212" t="n"/>
@@ -25458,13 +25458,13 @@
       </c>
       <c r="K278" s="211" t="n"/>
       <c r="L278" s="210" t="n"/>
-      <c r="M278" s="211" t="n"/>
+      <c r="M278" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N278" s="211" t="n"/>
-      <c r="O278" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O278" s="211" t="n"/>
       <c r="P278" s="211" t="n"/>
       <c r="Q278" s="233" t="n"/>
       <c r="R278" s="212" t="n"/>
@@ -25529,13 +25529,13 @@
       </c>
       <c r="K279" s="211" t="n"/>
       <c r="L279" s="210" t="n"/>
-      <c r="M279" s="211" t="n"/>
+      <c r="M279" s="211" t="inlineStr">
+        <is>
+          <t>K-</t>
+        </is>
+      </c>
       <c r="N279" s="211" t="n"/>
-      <c r="O279" s="211" t="inlineStr">
-        <is>
-          <t>K-</t>
-        </is>
-      </c>
+      <c r="O279" s="211" t="n"/>
       <c r="P279" s="211" t="n"/>
       <c r="Q279" s="233" t="n"/>
       <c r="R279" s="212" t="n"/>
@@ -25590,20 +25590,20 @@
       <c r="H280" s="211" t="n"/>
       <c r="I280" s="211" t="n"/>
       <c r="J280" s="211" t="n"/>
-      <c r="K280" s="211" t="n"/>
-      <c r="L280" s="210" t="inlineStr">
+      <c r="K280" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L280" s="210" t="n"/>
       <c r="M280" s="211" t="n"/>
-      <c r="N280" s="211" t="n"/>
+      <c r="N280" s="211" t="inlineStr">
+        <is>
+          <t>〇</t>
+        </is>
+      </c>
       <c r="O280" s="211" t="n"/>
-      <c r="P280" s="211" t="inlineStr">
-        <is>
-          <t>〇</t>
-        </is>
-      </c>
+      <c r="P280" s="211" t="n"/>
       <c r="Q280" s="233" t="n"/>
       <c r="R280" s="212" t="n"/>
       <c r="S280" s="233" t="n"/>
@@ -25788,13 +25788,13 @@
       </c>
       <c r="J283" s="211" t="n"/>
       <c r="K283" s="211" t="n"/>
-      <c r="L283" s="210" t="n"/>
+      <c r="L283" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M283" s="211" t="n"/>
-      <c r="N283" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N283" s="211" t="n"/>
       <c r="O283" s="211" t="n"/>
       <c r="P283" s="211" t="n"/>
       <c r="Q283" s="233" t="n"/>
@@ -25854,19 +25854,19 @@
         </is>
       </c>
       <c r="J284" s="211" t="n"/>
-      <c r="K284" s="211" t="n"/>
-      <c r="L284" s="210" t="inlineStr">
+      <c r="K284" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
-      <c r="M284" s="211" t="n"/>
+      <c r="L284" s="210" t="n"/>
+      <c r="M284" s="211" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N284" s="211" t="n"/>
-      <c r="O284" s="211" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O284" s="211" t="n"/>
       <c r="P284" s="211" t="n"/>
       <c r="Q284" s="233" t="n"/>
       <c r="R284" s="212" t="n"/>
@@ -25932,13 +25932,13 @@
       <c r="K285" s="211" t="n"/>
       <c r="L285" s="210" t="n"/>
       <c r="M285" s="211" t="n"/>
-      <c r="N285" s="211" t="n"/>
+      <c r="N285" s="211" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
       <c r="O285" s="211" t="n"/>
-      <c r="P285" s="211" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
+      <c r="P285" s="211" t="n"/>
       <c r="Q285" s="233" t="n"/>
       <c r="R285" s="212" t="n"/>
       <c r="S285" s="233" t="n"/>
@@ -25988,12 +25988,12 @@
       <c r="H286" s="211" t="n"/>
       <c r="I286" s="211" t="n"/>
       <c r="J286" s="211" t="n"/>
-      <c r="K286" s="211" t="n"/>
-      <c r="L286" s="210" t="inlineStr">
+      <c r="K286" s="211" t="inlineStr">
         <is>
           <t>K-</t>
         </is>
       </c>
+      <c r="L286" s="210" t="n"/>
       <c r="M286" s="211" t="n"/>
       <c r="N286" s="211" t="n"/>
       <c r="O286" s="211" t="n"/>
@@ -26056,13 +26056,13 @@
       </c>
       <c r="J287" s="211" t="n"/>
       <c r="K287" s="211" t="n"/>
-      <c r="L287" s="210" t="n"/>
+      <c r="L287" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M287" s="211" t="n"/>
-      <c r="N287" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N287" s="211" t="n"/>
       <c r="O287" s="211" t="n"/>
       <c r="P287" s="211" t="n"/>
       <c r="Q287" s="233" t="n"/>
@@ -26127,13 +26127,13 @@
       <c r="I288" s="211" t="n"/>
       <c r="J288" s="211" t="n"/>
       <c r="K288" s="211" t="n"/>
-      <c r="L288" s="210" t="n"/>
+      <c r="L288" s="210" t="inlineStr">
+        <is>
+          <t>N-</t>
+        </is>
+      </c>
       <c r="M288" s="211" t="n"/>
-      <c r="N288" s="211" t="inlineStr">
-        <is>
-          <t>N-</t>
-        </is>
-      </c>
+      <c r="N288" s="211" t="n"/>
       <c r="O288" s="211" t="n"/>
       <c r="P288" s="211" t="n"/>
       <c r="Q288" s="233" t="n"/>
@@ -26199,13 +26199,13 @@
       </c>
       <c r="K289" s="241" t="n"/>
       <c r="L289" s="242" t="n"/>
-      <c r="M289" s="241" t="n"/>
+      <c r="M289" s="241" t="inlineStr">
+        <is>
+          <t>M-</t>
+        </is>
+      </c>
       <c r="N289" s="241" t="n"/>
-      <c r="O289" s="241" t="inlineStr">
-        <is>
-          <t>M-</t>
-        </is>
-      </c>
+      <c r="O289" s="241" t="n"/>
       <c r="P289" s="241" t="n"/>
       <c r="Q289" s="229" t="n"/>
       <c r="R289" s="243" t="n"/>
@@ -27324,7 +27324,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="19.35" customHeight="1" s="252">
       <c r="A3" s="126" t="inlineStr">
         <is>
@@ -33372,7 +33371,6 @@
       <c r="R45" s="0" t="n"/>
       <c r="S45" s="0" t="n"/>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="K47" s="0" t="n"/>
     </row>
@@ -40014,7 +40012,6 @@
       <c r="R45" s="0" t="n"/>
       <c r="S45" s="0" t="n"/>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="K47" s="0" t="n"/>
     </row>
